--- a/data/geoparser_validation/geoparser_labelling_workbook.xlsx
+++ b/data/geoparser_validation/geoparser_labelling_workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\OneDrive\Desktop\Msc Data Science\Dissertation\Geoparser verification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{648F26E2-9B42-4ED0-B568-232BAFFEE19E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C784190A-EABB-4CDC-91F4-AF486FAA1DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1361" uniqueCount="845">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1389" uniqueCount="873">
   <si>
     <t>ReliefWeb geoparser validation: labelling instructions</t>
   </si>
@@ -3106,84 +3106,174 @@
     <t>Doolow;Belet Weyne;Bulo-Burte</t>
   </si>
   <si>
-    <t>Galdogob;Jariiban</t>
-  </si>
-  <si>
     <t>Jariiban written as Jariban in this report. Consider expanding alias list</t>
   </si>
   <si>
-    <t>several</t>
-  </si>
-  <si>
     <t>infographic</t>
   </si>
   <si>
-    <t>Belet Weyne; Afgooye; Mogadishu;Kismaayo;Doolow;Marka;Wanla Weyn;Gaalkacyo;Galdogob;Balcad</t>
-  </si>
-  <si>
     <t xml:space="preserve">Afgooye </t>
   </si>
   <si>
-    <t>Afmadow,Kismaayo</t>
-  </si>
-  <si>
-    <t>Banadir;Baydhaba;Afgooye;Doolow;Kismaayo</t>
-  </si>
-  <si>
     <t>https://reliefweb.int/node/4061769'</t>
   </si>
   <si>
-    <t>Banadir, Afgoye, Baidoa, Burhakabe, Merka, Kismayo, Jowhar,
-Mahaday, Beletweyn, Bulo Burte, Jalalaqsi, Hawadley Village in Bal’ad, Bosaso, Garowe, and
-Qardho, Borama, Burco, and South Galkacyo</t>
-  </si>
-  <si>
     <t>names copied and pasted as they are from reliefweb. Check naming and match with alias. Discard those not found in alias</t>
   </si>
   <si>
     <t>Badhaadhe ; Kismaayo</t>
   </si>
   <si>
-    <t>Afmadow </t>
-  </si>
-  <si>
     <t>Afgoye;Beletweyn;Buur Xakaba;Bossaso;Balcad</t>
   </si>
   <si>
-    <t>Bossaso; Balad; Garowe; Burhakabo; Gardo; Daynile; Mahaday; Banadir; Galgadud; Mudug; Mudug G; Hiiraan; Middle Shebelle; Lower Shabelle; Gedo; Lower Juba; Middle Juba; Ayn; Bari; Gardafuu; Karkaar; Nugaal; Sanaag; Sool; Bakool; Bay</t>
-  </si>
-  <si>
-    <t>Abudwak; Afmadow; Baidoa; Bardera; Beled Weyne; Berbera; Borama; Bossaso; Burao; Dhusamareb; Dinsor; Doblei; El Barde; Erigavo; Galkayo; Hargeisa; Hudur; Kismayo; Qorioley; Togwajale</t>
-  </si>
-  <si>
-    <t>Afgooye; Baydhaba; Hargeysa; Wanla Weyn; Marka; Laas Caanood; Jowhar; Balcad; Qoryooley; Buur Hakaba; Belet Weyne; Diinsoor; Gebiley; Berbera; Bulo Burto; Kismaayo; Baardheere; Gaalkacyo; Jalalaqsi; Garbahaarey; Luuq; Burco</t>
-  </si>
-  <si>
-    <t>mudug;gedo</t>
-  </si>
-  <si>
-    <t>Cabudwaaq; Dhuusamarreeb; Doolow; Galdogob; Hargeisa; Hobyo; Jariiban; Luuq; Qoryooley; Wajid; Xudur</t>
-  </si>
-  <si>
     <t>Bossaso; Balad; Garowe; Burhakabo; Gardo; Daynile (Mogadishu-Daynile); Mahaday; Mudug; Karkaar; Bay (Baydhaba/Baidoa); Gedo; Lower Juba (Kismaayo/Kismayo); Luuq; Doolow; Qoryooley; Xudun; Diinsoor; Borama; Cadaado; Jariiban; Laas Caanood; Mogadishu-Kaxda</t>
   </si>
   <si>
     <t>Mogadishu-Wadajir; Mogadishu-Waaberi; Mogadishu-Abdiaziz; Ceel Waaq; Garbahaarey; Hargeysa; Berbera; Afmadow; Jamaame; Marka; Wanla Weyn; Xudur; Banadir; Galgadud; Mudug G; Hiiraan; Middle Shebelle; Lower Shabelle; Middle Juba; Ayn; Bari; Gardafuu; Nugaal; Sanaag; Sool; Bakool</t>
   </si>
   <si>
-    <t>Hargeisa; Dila; Buhoodle; Xudun (Sool); Dollow; Belet Weyne; Luuq; Sablaale; Baraawe; Jamaame; Badhaadhe; Kismaayo; Jilib; Afgoye; Wanla Weyne; Garbaharey (Garbahaarey); Ceel Waaq; Dhuusamarreeb; Cabudwaaq; Ceel Dheer; Laas Canood (Las'Anod); Hobyo; Laasqoray; Bossaso; Cadaado; Ceel Buur; Bulo Burte (Bulle Burte); Jalalaqsi; Qoryooley; Kurtunwaarey; Baardheere (Bardheere); Saakow; Bualle; Afmadow; Dinsoor; Belet Xaawo; Lughaye; Zeylac; Baki; Berbera; Ceel Afweyn; Borama (Boorama); Gebiley (Gebilley); Qandala; Ceerigaabo; Sheikh; Wajaale; Jowhar</t>
-  </si>
-  <si>
-    <t>Malawle; Gumburaha; Aburiin; Dhubato; Gacan Libah; Gatiiley; Taysa; Elafweyn; Bur Hakaba; Baligubadle; Carmo; Garowe; Burtinle; Dararweyne; Baran; Odwayne; Qardho; Xasbahale; Darusalam; Widh widh; Ufayn; Dangaranyo; Uusgure; Dhahar; Murcaanyo; Galkacyo; Awdal; Woqooyi Galbeed; Togdheer; Sool; Sanaag; Bari; Nugaal; Mudug; Galgaduud; Hiraan; Middle Shabelle; Lower Shabelle; Banadir; Bay; Bakool; Gedo; Middle Juba; Lower Juba</t>
-  </si>
-  <si>
     <t>BAY</t>
   </si>
   <si>
     <t>Banadir; Afgoye; Baidoa; Burhakabe; Merka; Kismayo; Jowhar; Mahaday; Beletweyn; Bulo Burte; Jalalaqsi; Hawadley Village in Bal’ad; Bosaso; Garowe; Qardho</t>
   </si>
   <si>
-    <t>Aden Yabaal; Afgooye; Baardheere; Badhaadhe; Bakool; Balcad; Bandarbeyla; Baraawe; Baydhaba; Belet Xaawo; Belet Weyne; Berbera; Borama; Bossaso; Bulo Burto; Burco; Burtinle; Buuhoodle; Buur Hakaba; Cabudwaaq; Cadaado; Caluula; Caynabo; Ceel Afweyn; Ceel Barde; Ceel Buur; Ceel Dheer; Ceel Waaq; Ceerigaabo; Dhuusamarreeb; Diinsoor; Doolow; Eyl; Gaalkacyo; Garbahaarey; Garowe; Gebiley; Hargeysa; Hobyo; Iskushuban; Jalalaqsi; Jamaame; Jariiban; Jowhar; Kismaayo; Kurtunwaarey; Laas Caanood; Lughaye; Luuq; Mahas; Marka; Oodweyne; Qandala; Qansax Dheere; Qardho; Qoryooley; Rab Dhuure; Saakow; Sablaale; Taleex; Tijieglo; Waajid; Wanla Weyn; Xarardheere; Xudun; Xudur; Zeylac</t>
+    <t>Adan Yabal; Afgooye; Afmadow; Badhaadhe; Balcad; Bandarbeyla; Baraawe; Bardheere; Baydhaba; Belet Xaawo; Beletweyne; Berbera; Bondhere; Borama; Bossaso; Bulo Burto; Burco; Burtinle; Buuhoodle; Buur Hakaba; Bu'aale; Cabudwaaq; Cadaado; Cadale; Caluula; Caynabo; Ceel Afweyn; Ceel Barde; Ceel Buur; Ceel Dheer; Ceel Waaq; Ceerigaabo; Dayniile; Dharkenley; Dhuusamareeb; Diinsoor; Doolow; Eyl; Gaalkacyo; Garbaharey; Garoowe; Gebiley; Heliwa; Hobyo; Hodan; Iskushuban; Jalalaqsi; Jamaame; Jariiban; Jilib; Jowhar; Kismaayo; Kurtunwaarey; Laas Caanood; Laasqoray; Lughaye; Luuq; Marka; Owdweyne; Qandala; Qansax Dheere; Qardho; Qoryooley; Rabdhuree; Saakow; Sablaale; Shangani; Sheikh; Shibis; Taleex; Tayeeglow; Waajid; Wadajir; Wanla Weyn; Wardhigley; Xarardheere; Xudun; Xuduur; Yaaqshid; Zeylac</t>
+  </si>
+  <si>
+    <t>Baidoa; Balcad; Banadir; Buuhoodle; Jowhar; Kismayo; Laas Caanood; Luuq</t>
+  </si>
+  <si>
+    <t>Data type: report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data type: report
+names copied and pasted as they are from reliefweb. Check naming and match with alias. Discard those not found in alias. If a region name is also included, please discard it as well and only keep admin 2 </t>
+  </si>
+  <si>
+    <t>Data type: inforgraphic</t>
+  </si>
+  <si>
+    <t>Awdal, Bakool, Banadir, Bari, Bay, Galgaduud, Gedo, Hiraan, Lower Juba, Lower Shabelle, Middle Juba, Middle Shabelle, Mudug, Nugaal, Sanaag, Sool, Togdheer, and Woqooyi Galbeed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data type: infographic
+names copied and pasted as they are from reliefweb. Check naming and match with alias. Discard those not found in alias. If a region name is also included, please discard it as well and only keep admin 2 </t>
+  </si>
+  <si>
+    <t>Mataban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data type: news and press release
+Mataban district not included in original alias list. Please look up and see if this is an actual district. I looked it up online and it days it does. I also found that Mataaban is a way to spell it. </t>
+  </si>
+  <si>
+    <t>Baki; Balcad; Bardheere; Belet Weyne; Berbera; Bualle; Bulo Burte; Ceel Afweyn; Doolow; Iskushuban; Jalalaqsi; Jowhar; Lughaye; Luuq; Zeylac</t>
+  </si>
+  <si>
+    <t>Data type: Powerpoint presentation
+names copied and pasted as they are from reliefweb. Check naming and match with alias. Discard those not found in alias. If a region name is also included, please discard it as well and only keep admin 2</t>
+  </si>
+  <si>
+    <t>Abdul Aziz; Afgoye; Badhan; Baidoa; Balad; Banadir; Barawe; Belethawo; Beletweyne; Borama; Bondere; Bosaso; Bulo Burte; Burao; Burhakabe (Burhakabo); Danyile (Daynile); Dhahar; Dharkenly; Erigavo (Eigavo); Gabiley; Gardo; Garowe; Hamar jajab; Hamar weyn; Hargeisa; Hawadley Village; Hawl Wadag; Heliwa; Hodan; Jalalaqsi (Jalalaqso); Jowhar; Kahda; Karan; Kismayo; Kuntunwarey (Kurtunwaray); Lasqoray; Mahaday; Merka; Owdweyne; Qardho; Qoryoley; Shangani; Shibis; South Galkacyo (South Galkaio); Waberi; Wadajir; Wardegley; Yaqshid</t>
+  </si>
+  <si>
+    <t>Data type: Report
+names copied and pasted as they are from reliefweb. Check naming and match with alias. Discard those not found in alias. If a region name is also included, please discard it as well and only keep admin 2</t>
+  </si>
+  <si>
+    <t>Data type: Report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data type: news and press release
+ </t>
+  </si>
+  <si>
+    <t>Galdogob (Goldogob); Galkayo (Galkacyo); Jariban</t>
+  </si>
+  <si>
+    <t>Afgooye; Afmadow; Baardheere; Baidoa; Balcad; Belet Weyne; Belet Xaawo; Cabudwaaq; Dayniile; Dhuusamarreeb; Doolow; Gaalkacyo (Gaalkacye); Garoowe; Hobyo; Hodan; Jamaame; Jowhar; Kahda; Kismaayo; Luuq; Waajid; Xudur</t>
+  </si>
+  <si>
+    <t>Data type: Bulleting 
+names copied and pasted as they are from reliefweb. Check naming and match with alias. Discard those not found in alias. If a region name is also included, please discard it as well and only keep admin 2</t>
+  </si>
+  <si>
+    <t>Belet Weyne; Afgooye; Balcad; Dayniile; Kismayo; Doolow; Marka; Wanla Weyn; Jowhar; Gaalkacyo; Galdogob</t>
+  </si>
+  <si>
+    <t>Data type: assessment</t>
+  </si>
+  <si>
+    <t>Afmadow,Kismaayo; Jowhar; Beletweyne; Galdogob; Hargeysa</t>
+  </si>
+  <si>
+    <t>Banadir;Baydhaba;Afgooye;Doolow;Dhobley</t>
+  </si>
+  <si>
+    <t>Afgoye; Baidoa; Balad (Hawadley Village); Banadir; Beletweyne; Borama; Bosaso; Bulo Burte; Burao; Burhakabe; Danyile; Dhahar; Garowe; Jalalaqsi; Jowhar; Kismayo; Kuntunwarey; Mahaday; Merka; Qardho; South Galkacyo</t>
+  </si>
+  <si>
+    <t>Abdul Aziz; Badhan; Barawe; Belethawo; Bondere; Dharkenly; Erigavo; Gabiley; Hamar jajab; Hamar weyn; Hargeisa; Hawl Wadag; Heliwa; Hodan; Kahda; Karan; Lasqoray; Owdweyne; Qoryoley; Shangani; Shibis; Waberi; Wadajir; Wardegley; Yaqshid</t>
+  </si>
+  <si>
+    <t>Afmadow; Baardheere; Badhaadhe; Ceelwaaq; Dhobley; Dollow; Kismayo</t>
+  </si>
+  <si>
+    <t>Buurdhuubo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data type: Meeting summary </t>
+  </si>
+  <si>
+    <t>Afmadow;Dhobley;Kismaayo</t>
+  </si>
+  <si>
+    <t>Badhaadhe;Jamaame</t>
+  </si>
+  <si>
+    <t>Data type: news and press release</t>
+  </si>
+  <si>
+    <t>Data type: News and press release</t>
+  </si>
+  <si>
+    <t>Balad; Bossaso; Burhakabo; Daynile; Gardo; Garowe; Mahaday</t>
+  </si>
+  <si>
+    <t>Abudwak; Afmadow; Baidoa; Bardera; Beled Weyne; Borama; Bossaso; Burao; Dhusamareb; Dinsor; Doblei; El Barde; Erigavo; Galkayo; Hargeisa; Hudur; Kismayo; Qoriole</t>
+  </si>
+  <si>
+    <t>Berbera; Mogadishu; Togwajal</t>
+  </si>
+  <si>
+    <t>Afgooye; Afmadow; Baardheere (Bardheare); Baydhaba; Belet Weyne; Bulo Burti; Dollow; Gaalkacyo; Jariban; Jowhar; Luuq; Marka; Qardho</t>
+  </si>
+  <si>
+    <t>Balcad; Banadir; Berbera; Bualle; Burco; Buur Hakaba; Diinsoor; Garbahaarey; Gebiley; Hargeysa; Jalalaqsi; Kismaayo; Laas Caanood; Qoryooley; Wanla Weyn</t>
+  </si>
+  <si>
+    <t>Cabudwaaq; Dhuusamarreeb; Doolow; Galdogob; Hargeisa; Hobyo; Jariiban; Luuq; Mogadishu; Xudur</t>
+  </si>
+  <si>
+    <t>Qoryooley; Wajid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data type: infographic
+</t>
+  </si>
+  <si>
+    <t>Afmadow; Baki; Bardheere; Belet Weyne; Belet Xaawo; Berbera; Borama; Bossaso; Bualle; Buhoodle; Bulo Burte; Burao; Burhakaba; Burtinle; Cabudwaaq; Cadaado; Ceel Afweyn; Ceel Buur; Ceel Dheer; Ceel Waaq; Ceerigaabo; Dhahar; Dhuusamarreeb; Dinsoor; Dollow; Gaalkacyo; Garbahaarey; Garowe; Gebiley; Hargeisa; Hobyo; Jalalaqsi; Jamaame; Jilib; Jowhar; Kurtunwaarey; Laas Canood; Laasqoray; Lughaye; Luuq; Odwayne; Qandala; Qardho; Qoryooley; Saakow; Sablaale; Sheikh; Wanla Weyne; Xudun; Zeylac</t>
+  </si>
+  <si>
+    <t>Afgoye; Badhaadhe; Baraawe; Kismaayo; Mogadishu</t>
+  </si>
+  <si>
+    <t>Afgoye; Baidoa; Balad (Hawadley Village); Banadir; Beletweyn; Borama; Bosaso; Bossaso; Bulo Burte; Burhakabe; Burhakabo; Daynile; Dhahar; Gardo; Garowe; Jalalaqsi; Jowhar; Kismayo; Kuntunwarey; Mahaday; Merka; Qardho</t>
+  </si>
+  <si>
+    <t>Abdul Aziz; Badhan; Badhan SL; Barawe; Belethawo; Bondere; Burao; Danyile; Dhahar SL; Dharkenly; Eigavo; Erigavo; Gabiley; Hamar jajab; Hamar weyn; Hargeisa; Hawl Wadag; Heliwa; Hodan; Kahda; Karan; Kurtunwaray; Lasqoray; Owdweyne; Qoryoley; Shangani; Shibis; South Galkacyo; South Galkaio; Waberi; Wadajir; Wardegley; Yaqshid</t>
   </si>
 </sst>
 </file>
@@ -3202,35 +3292,42 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -3939,7 +4036,7 @@
       <c r="D4" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="13" t="s">
         <v>57</v>
       </c>
       <c r="F4" s="7" t="s">
@@ -3951,8 +4048,8 @@
       <c r="H4" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="I4" s="9" t="s">
-        <v>815</v>
+      <c r="I4" s="14" t="s">
+        <v>829</v>
       </c>
       <c r="J4" s="9" t="s">
         <v>815</v>
@@ -3960,7 +4057,9 @@
       <c r="K4" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="L4" s="9"/>
+      <c r="L4" s="14" t="s">
+        <v>833</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" s="7">
@@ -3994,7 +4093,9 @@
       <c r="K5" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="L5" s="9"/>
+      <c r="L5" s="9" t="s">
+        <v>834</v>
+      </c>
     </row>
     <row r="6" spans="1:12" ht="178.5" x14ac:dyDescent="0.45">
       <c r="A6" s="7">
@@ -4059,7 +4160,7 @@
       <c r="H7" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="I7" s="9" t="s">
         <v>597</v>
       </c>
       <c r="J7" s="15" t="s">
@@ -4068,7 +4169,9 @@
       <c r="K7" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="L7" s="9"/>
+      <c r="L7" s="9" t="s">
+        <v>832</v>
+      </c>
     </row>
     <row r="8" spans="1:12" ht="114.75" x14ac:dyDescent="0.45">
       <c r="A8" s="7">
@@ -4104,7 +4207,9 @@
       <c r="K8" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="L8" s="9"/>
+      <c r="L8" s="9" t="s">
+        <v>832</v>
+      </c>
     </row>
     <row r="9" spans="1:12" ht="357" x14ac:dyDescent="0.45">
       <c r="A9" s="7">
@@ -4140,9 +4245,11 @@
       <c r="K9" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="L9" s="9"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="L9" s="9" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="89.25" x14ac:dyDescent="0.45">
       <c r="A10" s="7">
         <v>8</v>
       </c>
@@ -4168,13 +4275,15 @@
       <c r="I10" s="15" t="s">
         <v>815</v>
       </c>
-      <c r="J10" s="15" t="s">
-        <v>49</v>
+      <c r="J10" s="14" t="s">
+        <v>835</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="9"/>
+      <c r="L10" s="14" t="s">
+        <v>836</v>
+      </c>
     </row>
     <row r="11" spans="1:12" ht="178.5" x14ac:dyDescent="0.45">
       <c r="A11" s="7">
@@ -4201,16 +4310,18 @@
       <c r="H11" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="I11" s="9" t="s">
+        <v>837</v>
+      </c>
+      <c r="J11" s="9" t="s">
         <v>815</v>
       </c>
-      <c r="J11" s="15" t="s">
-        <v>815</v>
-      </c>
       <c r="K11" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="L11" s="9"/>
+      <c r="L11" s="14" t="s">
+        <v>838</v>
+      </c>
     </row>
     <row r="12" spans="1:12" ht="165.75" x14ac:dyDescent="0.45">
       <c r="A12" s="7">
@@ -4240,15 +4351,17 @@
       <c r="I12" s="15" t="s">
         <v>818</v>
       </c>
-      <c r="J12" s="15" t="s">
-        <v>815</v>
+      <c r="J12" s="17" t="s">
+        <v>839</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="L12" s="9"/>
-    </row>
-    <row r="13" spans="1:12" ht="191.25" x14ac:dyDescent="0.45">
+      <c r="L12" s="14" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="280.5" x14ac:dyDescent="0.45">
       <c r="A13" s="7">
         <v>11</v>
       </c>
@@ -4273,10 +4386,18 @@
       <c r="H13" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
+      <c r="I13" s="14" t="s">
+        <v>841</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>842</v>
+      </c>
     </row>
     <row r="14" spans="1:12" ht="25.5" x14ac:dyDescent="0.45">
       <c r="A14" s="7">
@@ -4303,7 +4424,7 @@
       <c r="H14" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I14" s="14" t="s">
         <v>749</v>
       </c>
       <c r="J14" s="15" t="s">
@@ -4348,7 +4469,9 @@
       <c r="K15" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="L15" s="9"/>
+      <c r="L15" s="9" t="s">
+        <v>843</v>
+      </c>
     </row>
     <row r="16" spans="1:12" ht="216.75" x14ac:dyDescent="0.45">
       <c r="A16" s="7">
@@ -4384,7 +4507,9 @@
       <c r="K16" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="L16" s="9"/>
+      <c r="L16" s="14" t="s">
+        <v>844</v>
+      </c>
     </row>
     <row r="17" spans="1:12" ht="178.5" x14ac:dyDescent="0.45">
       <c r="A17" s="7">
@@ -4411,8 +4536,8 @@
       <c r="H17" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="I17" s="15" t="s">
-        <v>819</v>
+      <c r="I17" s="14" t="s">
+        <v>845</v>
       </c>
       <c r="J17" s="15" t="s">
         <v>815</v>
@@ -4421,7 +4546,7 @@
         <v>46</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="102" x14ac:dyDescent="0.45">
@@ -4449,12 +4574,20 @@
       <c r="H18" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="I18" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>846</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="L18" s="14" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="395.25" x14ac:dyDescent="0.45">
       <c r="A19" s="7">
         <v>17</v>
       </c>
@@ -4480,17 +4613,17 @@
       <c r="I19" s="9" t="s">
         <v>815</v>
       </c>
-      <c r="J19" s="9" t="s">
-        <v>821</v>
+      <c r="J19" s="14" t="s">
+        <v>830</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>46</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="38.25" x14ac:dyDescent="0.45">
       <c r="A20" s="7">
         <v>18</v>
       </c>
@@ -4516,14 +4649,14 @@
       <c r="I20" s="9" t="s">
         <v>815</v>
       </c>
-      <c r="J20" s="9" t="s">
-        <v>821</v>
+      <c r="J20" s="14" t="s">
+        <v>831</v>
       </c>
       <c r="K20" s="9" t="s">
         <v>46</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="204" x14ac:dyDescent="0.45">
@@ -4552,7 +4685,7 @@
         <v>122</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>823</v>
+        <v>848</v>
       </c>
       <c r="J21" s="9" t="s">
         <v>815</v>
@@ -4560,7 +4693,9 @@
       <c r="K21" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L21" s="9"/>
+      <c r="L21" s="14" t="s">
+        <v>847</v>
+      </c>
     </row>
     <row r="22" spans="1:12" ht="140.25" x14ac:dyDescent="0.45">
       <c r="A22" s="7">
@@ -4588,7 +4723,7 @@
         <v>126</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="J22" s="9" t="s">
         <v>815</v>
@@ -4596,7 +4731,9 @@
       <c r="K22" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L22" s="9"/>
+      <c r="L22" s="9" t="s">
+        <v>849</v>
+      </c>
     </row>
     <row r="23" spans="1:12" ht="89.25" x14ac:dyDescent="0.45">
       <c r="A23" s="7">
@@ -4632,9 +4769,11 @@
       <c r="K23" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L23" s="9"/>
-    </row>
-    <row r="24" spans="1:12" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="L23" s="9" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="38.25" x14ac:dyDescent="0.45">
       <c r="A24" s="7">
         <v>22</v>
       </c>
@@ -4659,16 +4798,18 @@
       <c r="H24" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="I24" s="9" t="s">
-        <v>825</v>
+      <c r="I24" s="14" t="s">
+        <v>850</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="K24" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L24" s="9"/>
+      <c r="L24" s="9" t="s">
+        <v>832</v>
+      </c>
     </row>
     <row r="25" spans="1:12" ht="63.75" x14ac:dyDescent="0.45">
       <c r="A25" s="7">
@@ -4704,7 +4845,9 @@
       <c r="K25" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="L25" s="9"/>
+      <c r="L25" s="9" t="s">
+        <v>832</v>
+      </c>
     </row>
     <row r="26" spans="1:12" ht="153" x14ac:dyDescent="0.45">
       <c r="A26" s="7">
@@ -4720,7 +4863,7 @@
         <v>140</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>45</v>
@@ -4762,16 +4905,16 @@
         <v>145</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>828</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>815</v>
+        <v>852</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>853</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L27" s="9" t="s">
-        <v>829</v>
+      <c r="L27" s="14" t="s">
+        <v>832</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="153" x14ac:dyDescent="0.45">
@@ -4799,11 +4942,11 @@
       <c r="H28" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="I28" s="9" t="s">
-        <v>815</v>
+      <c r="I28" s="14" t="s">
+        <v>854</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>815</v>
+        <v>855</v>
       </c>
       <c r="K28" s="9" t="s">
         <v>45</v>
@@ -4835,12 +4978,18 @@
       <c r="H29" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="I29" s="9"/>
+      <c r="I29" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="J29" s="9" t="s">
-        <v>830</v>
-      </c>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
+        <v>824</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>856</v>
+      </c>
     </row>
     <row r="30" spans="1:12" ht="204" x14ac:dyDescent="0.45">
       <c r="A30" s="7">
@@ -4868,15 +5017,17 @@
         <v>157</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>831</v>
-      </c>
-      <c r="J30" s="15" t="s">
-        <v>815</v>
+        <v>857</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>858</v>
       </c>
       <c r="K30" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="L30" s="9"/>
+      <c r="L30" s="9" t="s">
+        <v>832</v>
+      </c>
     </row>
     <row r="31" spans="1:12" ht="102" x14ac:dyDescent="0.45">
       <c r="A31" s="7">
@@ -4904,7 +5055,7 @@
         <v>161</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="J31" s="15" t="s">
         <v>815</v>
@@ -4912,7 +5063,9 @@
       <c r="K31" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="L31" s="9"/>
+      <c r="L31" s="9" t="s">
+        <v>859</v>
+      </c>
     </row>
     <row r="32" spans="1:12" ht="178.5" x14ac:dyDescent="0.45">
       <c r="A32" s="7">
@@ -5020,7 +5173,9 @@
       <c r="K34" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="L34" s="9"/>
+      <c r="L34" s="9" t="s">
+        <v>860</v>
+      </c>
     </row>
     <row r="35" spans="1:12" ht="140.25" x14ac:dyDescent="0.45">
       <c r="A35" s="7">
@@ -5047,17 +5202,17 @@
       <c r="H35" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="I35" s="15" t="s">
+      <c r="I35" s="14" t="s">
+        <v>861</v>
+      </c>
+      <c r="J35" s="14" t="s">
         <v>815</v>
       </c>
-      <c r="J35" s="17" t="s">
-        <v>833</v>
-      </c>
       <c r="K35" s="15" t="s">
         <v>46</v>
       </c>
       <c r="L35" s="17" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="89.25" x14ac:dyDescent="0.45">
@@ -5085,20 +5240,20 @@
       <c r="H36" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="I36" s="15" t="s">
-        <v>815</v>
+      <c r="I36" s="14" t="s">
+        <v>862</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>834</v>
+        <v>863</v>
       </c>
       <c r="K36" s="15" t="s">
         <v>46</v>
       </c>
       <c r="L36" s="17" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="114.75" x14ac:dyDescent="0.45">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="76.5" x14ac:dyDescent="0.45">
       <c r="A37" s="7">
         <v>35</v>
       </c>
@@ -5121,17 +5276,17 @@
         <v>46</v>
       </c>
       <c r="H37" s="8"/>
-      <c r="I37" s="15" t="s">
-        <v>815</v>
+      <c r="I37" s="14" t="s">
+        <v>864</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>835</v>
+        <v>865</v>
       </c>
       <c r="K37" s="15" t="s">
         <v>46</v>
       </c>
       <c r="L37" s="17" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="25.5" x14ac:dyDescent="0.45">
@@ -5270,11 +5425,11 @@
       <c r="I41" s="15" t="s">
         <v>815</v>
       </c>
-      <c r="J41" s="15" t="s">
-        <v>836</v>
-      </c>
-      <c r="K41" s="15" t="s">
-        <v>46</v>
+      <c r="J41" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="K41" s="9" t="s">
+        <v>45</v>
       </c>
       <c r="L41" s="9"/>
     </row>
@@ -5303,17 +5458,17 @@
       <c r="H42" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="I42" s="17" t="s">
-        <v>837</v>
-      </c>
-      <c r="J42" s="15" t="s">
-        <v>815</v>
+      <c r="I42" s="14" t="s">
+        <v>866</v>
+      </c>
+      <c r="J42" s="9" t="s">
+        <v>867</v>
       </c>
       <c r="K42" s="15" t="s">
         <v>46</v>
       </c>
       <c r="L42" s="17" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="140.25" x14ac:dyDescent="0.45">
@@ -5342,19 +5497,19 @@
         <v>205</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>838</v>
+        <v>826</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>839</v>
+        <v>827</v>
       </c>
       <c r="K43" s="15" t="s">
         <v>46</v>
       </c>
       <c r="L43" s="17" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.45">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="25.5" x14ac:dyDescent="0.45">
       <c r="A44" s="7">
         <v>42</v>
       </c>
@@ -5367,7 +5522,7 @@
       <c r="D44" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="E44" s="7" t="s">
+      <c r="E44" s="13" t="s">
         <v>207</v>
       </c>
       <c r="F44" s="7" t="s">
@@ -5377,12 +5532,18 @@
         <v>46</v>
       </c>
       <c r="H44" s="8"/>
-      <c r="I44" s="9"/>
-      <c r="J44" s="9"/>
+      <c r="I44" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="J44" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K44" s="9"/>
-      <c r="L44" s="9"/>
-    </row>
-    <row r="45" spans="1:12" ht="293.25" x14ac:dyDescent="0.45">
+      <c r="L44" s="14" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="255" x14ac:dyDescent="0.45">
       <c r="A45" s="7">
         <v>43</v>
       </c>
@@ -5407,14 +5568,14 @@
       <c r="H45" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="I45" s="17" t="s">
-        <v>840</v>
-      </c>
-      <c r="J45" s="17" t="s">
-        <v>841</v>
-      </c>
-      <c r="K45" s="15" t="s">
-        <v>45</v>
+      <c r="I45" s="14" t="s">
+        <v>869</v>
+      </c>
+      <c r="J45" s="14" t="s">
+        <v>870</v>
+      </c>
+      <c r="K45" s="9" t="s">
+        <v>46</v>
       </c>
       <c r="L45" s="9"/>
     </row>
@@ -5482,19 +5643,19 @@
         <v>218</v>
       </c>
       <c r="I47" s="14" t="s">
-        <v>843</v>
+        <v>871</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>815</v>
+        <v>872</v>
       </c>
       <c r="K47" s="9" t="s">
         <v>46</v>
       </c>
       <c r="L47" s="17" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="331.5" x14ac:dyDescent="0.45">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="102" x14ac:dyDescent="0.45">
       <c r="A48" s="7">
         <v>46</v>
       </c>
@@ -5519,18 +5680,10 @@
       <c r="H48" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="I48" s="9" t="s">
-        <v>815</v>
-      </c>
-      <c r="J48" s="14" t="s">
-        <v>844</v>
-      </c>
-      <c r="K48" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="L48" s="17" t="s">
-        <v>829</v>
-      </c>
+      <c r="I48" s="9"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="17"/>
     </row>
     <row r="49" spans="1:12" ht="178.5" x14ac:dyDescent="0.45">
       <c r="A49" s="7">
@@ -5562,7 +5715,7 @@
       <c r="K49" s="9"/>
       <c r="L49" s="9"/>
     </row>
-    <row r="50" spans="1:12" ht="369.75" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:12" ht="280.5" x14ac:dyDescent="0.45">
       <c r="A50" s="7">
         <v>48</v>
       </c>
@@ -5592,7 +5745,7 @@
       <c r="K50" s="9"/>
       <c r="L50" s="9"/>
     </row>
-    <row r="51" spans="1:12" ht="216.75" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:12" ht="153" x14ac:dyDescent="0.45">
       <c r="A51" s="7">
         <v>49</v>
       </c>
@@ -5622,7 +5775,7 @@
       <c r="K51" s="9"/>
       <c r="L51" s="9"/>
     </row>
-    <row r="52" spans="1:12" ht="242.25" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:12" ht="204" x14ac:dyDescent="0.45">
       <c r="A52" s="7">
         <v>50</v>
       </c>
@@ -5652,7 +5805,7 @@
       <c r="K52" s="9"/>
       <c r="L52" s="9"/>
     </row>
-    <row r="53" spans="1:12" ht="114.75" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:12" ht="76.5" x14ac:dyDescent="0.45">
       <c r="A53" s="7">
         <v>51</v>
       </c>
@@ -5682,7 +5835,7 @@
       <c r="K53" s="9"/>
       <c r="L53" s="9"/>
     </row>
-    <row r="54" spans="1:12" ht="153" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:12" ht="114.75" x14ac:dyDescent="0.45">
       <c r="A54" s="7">
         <v>52</v>
       </c>
@@ -5712,7 +5865,7 @@
       <c r="K54" s="9"/>
       <c r="L54" s="9"/>
     </row>
-    <row r="55" spans="1:12" ht="114.75" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:12" ht="89.25" x14ac:dyDescent="0.45">
       <c r="A55" s="7">
         <v>53</v>
       </c>
@@ -5770,7 +5923,7 @@
       <c r="K56" s="9"/>
       <c r="L56" s="9"/>
     </row>
-    <row r="57" spans="1:12" ht="25.5" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A57" s="7">
         <v>55</v>
       </c>
@@ -5828,7 +5981,7 @@
       <c r="K58" s="9"/>
       <c r="L58" s="9"/>
     </row>
-    <row r="59" spans="1:12" ht="382.5" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:12" ht="306" x14ac:dyDescent="0.45">
       <c r="A59" s="7">
         <v>57</v>
       </c>
@@ -5858,7 +6011,7 @@
       <c r="K59" s="9"/>
       <c r="L59" s="9"/>
     </row>
-    <row r="60" spans="1:12" ht="318.75" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:12" ht="229.5" x14ac:dyDescent="0.45">
       <c r="A60" s="7">
         <v>58</v>
       </c>
@@ -5916,7 +6069,7 @@
       <c r="K61" s="9"/>
       <c r="L61" s="9"/>
     </row>
-    <row r="62" spans="1:12" ht="318.75" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:12" ht="242.25" x14ac:dyDescent="0.45">
       <c r="A62" s="7">
         <v>60</v>
       </c>
@@ -5974,7 +6127,7 @@
       <c r="K63" s="9"/>
       <c r="L63" s="9"/>
     </row>
-    <row r="64" spans="1:12" ht="229.5" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:12" ht="165.75" x14ac:dyDescent="0.45">
       <c r="A64" s="7">
         <v>62</v>
       </c>
@@ -6090,7 +6243,7 @@
       <c r="K67" s="9"/>
       <c r="L67" s="9"/>
     </row>
-    <row r="68" spans="1:12" ht="204" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:12" ht="140.25" x14ac:dyDescent="0.45">
       <c r="A68" s="7">
         <v>66</v>
       </c>
@@ -6148,7 +6301,7 @@
       <c r="K69" s="9"/>
       <c r="L69" s="9"/>
     </row>
-    <row r="70" spans="1:12" ht="191.25" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:12" ht="114.75" x14ac:dyDescent="0.45">
       <c r="A70" s="7">
         <v>68</v>
       </c>
@@ -6234,7 +6387,7 @@
       <c r="K72" s="9"/>
       <c r="L72" s="9"/>
     </row>
-    <row r="73" spans="1:12" ht="114.75" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:12" ht="89.25" x14ac:dyDescent="0.45">
       <c r="A73" s="7">
         <v>71</v>
       </c>
@@ -6264,7 +6417,7 @@
       <c r="K73" s="9"/>
       <c r="L73" s="9"/>
     </row>
-    <row r="74" spans="1:12" ht="229.5" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:12" ht="140.25" x14ac:dyDescent="0.45">
       <c r="A74" s="7">
         <v>72</v>
       </c>
@@ -6294,7 +6447,7 @@
       <c r="K74" s="9"/>
       <c r="L74" s="9"/>
     </row>
-    <row r="75" spans="1:12" ht="293.25" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:12" ht="216.75" x14ac:dyDescent="0.45">
       <c r="A75" s="7">
         <v>73</v>
       </c>
@@ -6324,7 +6477,7 @@
       <c r="K75" s="9"/>
       <c r="L75" s="9"/>
     </row>
-    <row r="76" spans="1:12" ht="293.25" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:12" ht="204" x14ac:dyDescent="0.45">
       <c r="A76" s="7">
         <v>74</v>
       </c>
@@ -6414,7 +6567,7 @@
       <c r="K78" s="9"/>
       <c r="L78" s="9"/>
     </row>
-    <row r="79" spans="1:12" ht="242.25" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:12" ht="165.75" x14ac:dyDescent="0.45">
       <c r="A79" s="7">
         <v>77</v>
       </c>
@@ -6444,7 +6597,7 @@
       <c r="K79" s="9"/>
       <c r="L79" s="9"/>
     </row>
-    <row r="80" spans="1:12" ht="127.5" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:12" ht="89.25" x14ac:dyDescent="0.45">
       <c r="A80" s="7">
         <v>78</v>
       </c>
@@ -6474,7 +6627,7 @@
       <c r="K80" s="9"/>
       <c r="L80" s="9"/>
     </row>
-    <row r="81" spans="1:12" ht="38.25" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:12" ht="25.5" x14ac:dyDescent="0.45">
       <c r="A81" s="7">
         <v>79</v>
       </c>
@@ -6504,7 +6657,7 @@
       <c r="K81" s="9"/>
       <c r="L81" s="9"/>
     </row>
-    <row r="82" spans="1:12" ht="280.5" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:12" ht="204" x14ac:dyDescent="0.45">
       <c r="A82" s="7">
         <v>80</v>
       </c>
@@ -6534,7 +6687,7 @@
       <c r="K82" s="9"/>
       <c r="L82" s="9"/>
     </row>
-    <row r="83" spans="1:12" ht="331.5" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:12" ht="255" x14ac:dyDescent="0.45">
       <c r="A83" s="7">
         <v>81</v>
       </c>
@@ -6564,7 +6717,7 @@
       <c r="K83" s="9"/>
       <c r="L83" s="9"/>
     </row>
-    <row r="84" spans="1:12" ht="242.25" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:12" ht="153" x14ac:dyDescent="0.45">
       <c r="A84" s="7">
         <v>82</v>
       </c>
@@ -6594,7 +6747,7 @@
       <c r="K84" s="9"/>
       <c r="L84" s="9"/>
     </row>
-    <row r="85" spans="1:12" ht="267.75" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:12" ht="191.25" x14ac:dyDescent="0.45">
       <c r="A85" s="7">
         <v>83</v>
       </c>
@@ -6624,7 +6777,7 @@
       <c r="K85" s="9"/>
       <c r="L85" s="9"/>
     </row>
-    <row r="86" spans="1:12" ht="280.5" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:12" ht="255" x14ac:dyDescent="0.45">
       <c r="A86" s="7">
         <v>84</v>
       </c>
@@ -6654,7 +6807,7 @@
       <c r="K86" s="9"/>
       <c r="L86" s="9"/>
     </row>
-    <row r="87" spans="1:12" ht="267.75" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:12" ht="191.25" x14ac:dyDescent="0.45">
       <c r="A87" s="7">
         <v>85</v>
       </c>
@@ -6712,7 +6865,7 @@
       <c r="K88" s="9"/>
       <c r="L88" s="9"/>
     </row>
-    <row r="89" spans="1:12" ht="242.25" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:12" ht="178.5" x14ac:dyDescent="0.45">
       <c r="A89" s="7">
         <v>87</v>
       </c>
@@ -6742,7 +6895,7 @@
       <c r="K89" s="9"/>
       <c r="L89" s="9"/>
     </row>
-    <row r="90" spans="1:12" ht="267.75" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:12" ht="178.5" x14ac:dyDescent="0.45">
       <c r="A90" s="7">
         <v>88</v>
       </c>
@@ -6800,7 +6953,7 @@
       <c r="K91" s="9"/>
       <c r="L91" s="9"/>
     </row>
-    <row r="92" spans="1:12" ht="127.5" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:12" ht="102" x14ac:dyDescent="0.45">
       <c r="A92" s="7">
         <v>90</v>
       </c>
@@ -6830,7 +6983,7 @@
       <c r="K92" s="9"/>
       <c r="L92" s="9"/>
     </row>
-    <row r="93" spans="1:12" ht="267.75" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:12" ht="191.25" x14ac:dyDescent="0.45">
       <c r="A93" s="7">
         <v>91</v>
       </c>
@@ -6860,7 +7013,7 @@
       <c r="K93" s="9"/>
       <c r="L93" s="9"/>
     </row>
-    <row r="94" spans="1:12" ht="318.75" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:12" ht="242.25" x14ac:dyDescent="0.45">
       <c r="A94" s="7">
         <v>92</v>
       </c>
@@ -6890,7 +7043,7 @@
       <c r="K94" s="9"/>
       <c r="L94" s="9"/>
     </row>
-    <row r="95" spans="1:12" ht="242.25" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:12" ht="165.75" x14ac:dyDescent="0.45">
       <c r="A95" s="7">
         <v>93</v>
       </c>
@@ -6920,7 +7073,7 @@
       <c r="K95" s="9"/>
       <c r="L95" s="9"/>
     </row>
-    <row r="96" spans="1:12" ht="165.75" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:12" ht="127.5" x14ac:dyDescent="0.45">
       <c r="A96" s="7">
         <v>94</v>
       </c>
@@ -6950,7 +7103,7 @@
       <c r="K96" s="9"/>
       <c r="L96" s="9"/>
     </row>
-    <row r="97" spans="1:12" ht="102" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:12" ht="89.25" x14ac:dyDescent="0.45">
       <c r="A97" s="7">
         <v>95</v>
       </c>
@@ -6980,7 +7133,7 @@
       <c r="K97" s="9"/>
       <c r="L97" s="9"/>
     </row>
-    <row r="98" spans="1:12" ht="140.25" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:12" ht="102" x14ac:dyDescent="0.45">
       <c r="A98" s="7">
         <v>96</v>
       </c>
@@ -7010,7 +7163,7 @@
       <c r="K98" s="9"/>
       <c r="L98" s="9"/>
     </row>
-    <row r="99" spans="1:12" ht="255" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:12" ht="178.5" x14ac:dyDescent="0.45">
       <c r="A99" s="7">
         <v>97</v>
       </c>
@@ -7070,7 +7223,7 @@
       <c r="K100" s="9"/>
       <c r="L100" s="9"/>
     </row>
-    <row r="101" spans="1:12" ht="165.75" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:12" ht="153" x14ac:dyDescent="0.45">
       <c r="A101" s="7">
         <v>99</v>
       </c>
@@ -7100,7 +7253,7 @@
       <c r="K101" s="9"/>
       <c r="L101" s="9"/>
     </row>
-    <row r="102" spans="1:12" ht="204" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:12" ht="140.25" x14ac:dyDescent="0.45">
       <c r="A102" s="7">
         <v>100</v>
       </c>
@@ -7130,7 +7283,7 @@
       <c r="K102" s="9"/>
       <c r="L102" s="9"/>
     </row>
-    <row r="103" spans="1:12" ht="153" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:12" ht="102" x14ac:dyDescent="0.45">
       <c r="A103" s="7">
         <v>101</v>
       </c>
@@ -7188,7 +7341,7 @@
       <c r="K104" s="9"/>
       <c r="L104" s="9"/>
     </row>
-    <row r="105" spans="1:12" ht="280.5" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:12" ht="178.5" x14ac:dyDescent="0.45">
       <c r="A105" s="7">
         <v>103</v>
       </c>
@@ -7218,7 +7371,7 @@
       <c r="K105" s="9"/>
       <c r="L105" s="9"/>
     </row>
-    <row r="106" spans="1:12" ht="165.75" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:12" ht="127.5" x14ac:dyDescent="0.45">
       <c r="A106" s="7">
         <v>104</v>
       </c>
@@ -7248,7 +7401,7 @@
       <c r="K106" s="9"/>
       <c r="L106" s="9"/>
     </row>
-    <row r="107" spans="1:12" ht="165.75" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:12" ht="102" x14ac:dyDescent="0.45">
       <c r="A107" s="7">
         <v>105</v>
       </c>
@@ -7308,7 +7461,7 @@
       <c r="K108" s="9"/>
       <c r="L108" s="9"/>
     </row>
-    <row r="109" spans="1:12" ht="178.5" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:12" ht="102" x14ac:dyDescent="0.45">
       <c r="A109" s="7">
         <v>107</v>
       </c>
@@ -7338,7 +7491,7 @@
       <c r="K109" s="9"/>
       <c r="L109" s="9"/>
     </row>
-    <row r="110" spans="1:12" ht="216.75" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:12" ht="165.75" x14ac:dyDescent="0.45">
       <c r="A110" s="7">
         <v>108</v>
       </c>
@@ -7396,7 +7549,7 @@
       <c r="K111" s="9"/>
       <c r="L111" s="9"/>
     </row>
-    <row r="112" spans="1:12" ht="102" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:12" ht="63.75" x14ac:dyDescent="0.45">
       <c r="A112" s="7">
         <v>110</v>
       </c>
@@ -7456,7 +7609,7 @@
       <c r="K113" s="9"/>
       <c r="L113" s="9"/>
     </row>
-    <row r="114" spans="1:12" ht="153" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:12" ht="114.75" x14ac:dyDescent="0.45">
       <c r="A114" s="7">
         <v>112</v>
       </c>
@@ -7516,7 +7669,7 @@
       <c r="K115" s="9"/>
       <c r="L115" s="9"/>
     </row>
-    <row r="116" spans="1:12" ht="204" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:12" ht="165.75" x14ac:dyDescent="0.45">
       <c r="A116" s="7">
         <v>114</v>
       </c>
@@ -7574,7 +7727,7 @@
       <c r="K117" s="9"/>
       <c r="L117" s="9"/>
     </row>
-    <row r="118" spans="1:12" ht="229.5" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:12" ht="153" x14ac:dyDescent="0.45">
       <c r="A118" s="7">
         <v>116</v>
       </c>
@@ -7604,7 +7757,7 @@
       <c r="K118" s="9"/>
       <c r="L118" s="9"/>
     </row>
-    <row r="119" spans="1:12" ht="38.25" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:12" ht="25.5" x14ac:dyDescent="0.45">
       <c r="A119" s="7">
         <v>117</v>
       </c>
@@ -7634,7 +7787,7 @@
       <c r="K119" s="9"/>
       <c r="L119" s="9"/>
     </row>
-    <row r="120" spans="1:12" ht="140.25" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:12" ht="89.25" x14ac:dyDescent="0.45">
       <c r="A120" s="7">
         <v>118</v>
       </c>
@@ -7694,7 +7847,7 @@
       <c r="K121" s="9"/>
       <c r="L121" s="9"/>
     </row>
-    <row r="122" spans="1:12" ht="165.75" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:12" ht="102" x14ac:dyDescent="0.45">
       <c r="A122" s="7">
         <v>120</v>
       </c>
@@ -7724,7 +7877,7 @@
       <c r="K122" s="9"/>
       <c r="L122" s="9"/>
     </row>
-    <row r="123" spans="1:12" ht="293.25" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:12" ht="242.25" x14ac:dyDescent="0.45">
       <c r="A123" s="7">
         <v>121</v>
       </c>
@@ -7784,7 +7937,7 @@
       <c r="K124" s="9"/>
       <c r="L124" s="9"/>
     </row>
-    <row r="125" spans="1:12" ht="242.25" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:12" ht="178.5" x14ac:dyDescent="0.45">
       <c r="A125" s="7">
         <v>123</v>
       </c>
@@ -7814,7 +7967,7 @@
       <c r="K125" s="9"/>
       <c r="L125" s="9"/>
     </row>
-    <row r="126" spans="1:12" ht="318.75" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:12" ht="267.75" x14ac:dyDescent="0.45">
       <c r="A126" s="7">
         <v>124</v>
       </c>
@@ -7874,7 +8027,7 @@
       <c r="K127" s="9"/>
       <c r="L127" s="9"/>
     </row>
-    <row r="128" spans="1:12" ht="293.25" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:12" ht="255" x14ac:dyDescent="0.45">
       <c r="A128" s="7">
         <v>126</v>
       </c>
@@ -7932,7 +8085,7 @@
       <c r="K129" s="9"/>
       <c r="L129" s="9"/>
     </row>
-    <row r="130" spans="1:12" ht="204" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:12" ht="140.25" x14ac:dyDescent="0.45">
       <c r="A130" s="7">
         <v>128</v>
       </c>
@@ -7990,7 +8143,7 @@
       <c r="K131" s="9"/>
       <c r="L131" s="9"/>
     </row>
-    <row r="132" spans="1:12" ht="318.75" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:12" ht="242.25" x14ac:dyDescent="0.45">
       <c r="A132" s="7">
         <v>130</v>
       </c>
@@ -8020,7 +8173,7 @@
       <c r="K132" s="9"/>
       <c r="L132" s="9"/>
     </row>
-    <row r="133" spans="1:12" ht="267.75" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:12" ht="191.25" x14ac:dyDescent="0.45">
       <c r="A133" s="7">
         <v>131</v>
       </c>
@@ -8050,7 +8203,7 @@
       <c r="K133" s="9"/>
       <c r="L133" s="9"/>
     </row>
-    <row r="134" spans="1:12" ht="216.75" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:12" ht="191.25" x14ac:dyDescent="0.45">
       <c r="A134" s="7">
         <v>132</v>
       </c>
@@ -8108,7 +8261,7 @@
       <c r="K135" s="9"/>
       <c r="L135" s="9"/>
     </row>
-    <row r="136" spans="1:12" ht="255" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:12" ht="178.5" x14ac:dyDescent="0.45">
       <c r="A136" s="7">
         <v>134</v>
       </c>
@@ -8138,7 +8291,7 @@
       <c r="K136" s="9"/>
       <c r="L136" s="9"/>
     </row>
-    <row r="137" spans="1:12" ht="89.25" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:12" ht="51" x14ac:dyDescent="0.45">
       <c r="A137" s="7">
         <v>135</v>
       </c>
@@ -8168,7 +8321,7 @@
       <c r="K137" s="9"/>
       <c r="L137" s="9"/>
     </row>
-    <row r="138" spans="1:12" ht="369.75" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:12" ht="267.75" x14ac:dyDescent="0.45">
       <c r="A138" s="7">
         <v>136</v>
       </c>
@@ -8198,7 +8351,7 @@
       <c r="K138" s="9"/>
       <c r="L138" s="9"/>
     </row>
-    <row r="139" spans="1:12" ht="51" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:12" ht="25.5" x14ac:dyDescent="0.45">
       <c r="A139" s="7">
         <v>137</v>
       </c>
@@ -8228,7 +8381,7 @@
       <c r="K139" s="9"/>
       <c r="L139" s="9"/>
     </row>
-    <row r="140" spans="1:12" ht="63.75" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:12" ht="51" x14ac:dyDescent="0.45">
       <c r="A140" s="7">
         <v>138</v>
       </c>
@@ -8258,7 +8411,7 @@
       <c r="K140" s="9"/>
       <c r="L140" s="9"/>
     </row>
-    <row r="141" spans="1:12" ht="114.75" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:12" ht="89.25" x14ac:dyDescent="0.45">
       <c r="A141" s="7">
         <v>139</v>
       </c>
@@ -8346,7 +8499,7 @@
       <c r="K143" s="9"/>
       <c r="L143" s="9"/>
     </row>
-    <row r="144" spans="1:12" ht="255" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:12" ht="191.25" x14ac:dyDescent="0.45">
       <c r="A144" s="7">
         <v>142</v>
       </c>
@@ -8376,7 +8529,7 @@
       <c r="K144" s="9"/>
       <c r="L144" s="9"/>
     </row>
-    <row r="145" spans="1:12" ht="102" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:12" ht="63.75" x14ac:dyDescent="0.45">
       <c r="A145" s="7">
         <v>143</v>
       </c>
@@ -8406,7 +8559,7 @@
       <c r="K145" s="9"/>
       <c r="L145" s="9"/>
     </row>
-    <row r="146" spans="1:12" ht="318.75" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:12" ht="242.25" x14ac:dyDescent="0.45">
       <c r="A146" s="7">
         <v>144</v>
       </c>
@@ -8464,7 +8617,7 @@
       <c r="K147" s="9"/>
       <c r="L147" s="9"/>
     </row>
-    <row r="148" spans="1:12" ht="280.5" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:12" ht="204" x14ac:dyDescent="0.45">
       <c r="A148" s="7">
         <v>146</v>
       </c>
@@ -8494,7 +8647,7 @@
       <c r="K148" s="9"/>
       <c r="L148" s="9"/>
     </row>
-    <row r="149" spans="1:12" ht="165.75" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:12" ht="102" x14ac:dyDescent="0.45">
       <c r="A149" s="7">
         <v>147</v>
       </c>
@@ -8524,7 +8677,7 @@
       <c r="K149" s="9"/>
       <c r="L149" s="9"/>
     </row>
-    <row r="150" spans="1:12" ht="255" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:12" ht="191.25" x14ac:dyDescent="0.45">
       <c r="A150" s="7">
         <v>148</v>
       </c>
@@ -8554,7 +8707,7 @@
       <c r="K150" s="9"/>
       <c r="L150" s="9"/>
     </row>
-    <row r="151" spans="1:12" ht="255" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:12" ht="178.5" x14ac:dyDescent="0.45">
       <c r="A151" s="7">
         <v>149</v>
       </c>
@@ -8662,9 +8815,11 @@
     <hyperlink ref="E47" r:id="rId44" xr:uid="{34F40CD1-27E0-43CB-8C04-8EAC0B280D30}"/>
     <hyperlink ref="E48" r:id="rId45" xr:uid="{E1EEC388-F74D-4974-A4F9-4AE2FCD642DF}"/>
     <hyperlink ref="E49" r:id="rId46" xr:uid="{1C8774A2-A9A1-4F43-98F6-C951B8423B16}"/>
+    <hyperlink ref="E4" r:id="rId47" xr:uid="{E8146D32-CBAE-417B-AA12-BA90E9334704}"/>
+    <hyperlink ref="E44" r:id="rId48" xr:uid="{2F1D026A-CF24-42C1-B8D0-B911D595C828}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId47"/>
+  <pageSetup orientation="portrait" r:id="rId49"/>
 </worksheet>
 </file>
 
@@ -9261,7 +9416,7 @@
         <v>718</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="D42" s="11" t="s">
         <v>719</v>

--- a/data/geoparser_validation/geoparser_labelling_workbook.xlsx
+++ b/data/geoparser_validation/geoparser_labelling_workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\OneDrive\Desktop\Msc Data Science\Dissertation\Geoparser verification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C784190A-EABB-4CDC-91F4-AF486FAA1DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{670AD2FD-D41A-424F-BEF6-452A9DB33148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1389" uniqueCount="873">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="911">
   <si>
     <t>ReliefWeb geoparser validation: labelling instructions</t>
   </si>
@@ -3127,12 +3127,6 @@
     <t>Afgoye;Beletweyn;Buur Xakaba;Bossaso;Balcad</t>
   </si>
   <si>
-    <t>Bossaso; Balad; Garowe; Burhakabo; Gardo; Daynile (Mogadishu-Daynile); Mahaday; Mudug; Karkaar; Bay (Baydhaba/Baidoa); Gedo; Lower Juba (Kismaayo/Kismayo); Luuq; Doolow; Qoryooley; Xudun; Diinsoor; Borama; Cadaado; Jariiban; Laas Caanood; Mogadishu-Kaxda</t>
-  </si>
-  <si>
-    <t>Mogadishu-Wadajir; Mogadishu-Waaberi; Mogadishu-Abdiaziz; Ceel Waaq; Garbahaarey; Hargeysa; Berbera; Afmadow; Jamaame; Marka; Wanla Weyn; Xudur; Banadir; Galgadud; Mudug G; Hiiraan; Middle Shebelle; Lower Shabelle; Middle Juba; Ayn; Bari; Gardafuu; Nugaal; Sanaag; Sool; Bakool</t>
-  </si>
-  <si>
     <t>BAY</t>
   </si>
   <si>
@@ -3140,9 +3134,6 @@
   </si>
   <si>
     <t>Adan Yabal; Afgooye; Afmadow; Badhaadhe; Balcad; Bandarbeyla; Baraawe; Bardheere; Baydhaba; Belet Xaawo; Beletweyne; Berbera; Bondhere; Borama; Bossaso; Bulo Burto; Burco; Burtinle; Buuhoodle; Buur Hakaba; Bu'aale; Cabudwaaq; Cadaado; Cadale; Caluula; Caynabo; Ceel Afweyn; Ceel Barde; Ceel Buur; Ceel Dheer; Ceel Waaq; Ceerigaabo; Dayniile; Dharkenley; Dhuusamareeb; Diinsoor; Doolow; Eyl; Gaalkacyo; Garbaharey; Garoowe; Gebiley; Heliwa; Hobyo; Hodan; Iskushuban; Jalalaqsi; Jamaame; Jariiban; Jilib; Jowhar; Kismaayo; Kurtunwaarey; Laas Caanood; Laasqoray; Lughaye; Luuq; Marka; Owdweyne; Qandala; Qansax Dheere; Qardho; Qoryooley; Rabdhuree; Saakow; Sablaale; Shangani; Sheikh; Shibis; Taleex; Tayeeglow; Waajid; Wadajir; Wanla Weyn; Wardhigley; Xarardheere; Xudun; Xuduur; Yaaqshid; Zeylac</t>
-  </si>
-  <si>
-    <t>Baidoa; Balcad; Banadir; Buuhoodle; Jowhar; Kismayo; Laas Caanood; Luuq</t>
   </si>
   <si>
     <t>Data type: report</t>
@@ -3212,12 +3203,6 @@
     <t>Banadir;Baydhaba;Afgooye;Doolow;Dhobley</t>
   </si>
   <si>
-    <t>Afgoye; Baidoa; Balad (Hawadley Village); Banadir; Beletweyne; Borama; Bosaso; Bulo Burte; Burao; Burhakabe; Danyile; Dhahar; Garowe; Jalalaqsi; Jowhar; Kismayo; Kuntunwarey; Mahaday; Merka; Qardho; South Galkacyo</t>
-  </si>
-  <si>
-    <t>Abdul Aziz; Badhan; Barawe; Belethawo; Bondere; Dharkenly; Erigavo; Gabiley; Hamar jajab; Hamar weyn; Hargeisa; Hawl Wadag; Heliwa; Hodan; Kahda; Karan; Lasqoray; Owdweyne; Qoryoley; Shangani; Shibis; Waberi; Wadajir; Wardegley; Yaqshid</t>
-  </si>
-  <si>
     <t>Afmadow; Baardheere; Badhaadhe; Ceelwaaq; Dhobley; Dollow; Kismayo</t>
   </si>
   <si>
@@ -3274,6 +3259,135 @@
   </si>
   <si>
     <t>Abdul Aziz; Badhan; Badhan SL; Barawe; Belethawo; Bondere; Burao; Danyile; Dhahar SL; Dharkenly; Eigavo; Erigavo; Gabiley; Hamar jajab; Hamar weyn; Hargeisa; Hawl Wadag; Heliwa; Hodan; Kahda; Karan; Kurtunwaray; Lasqoray; Owdweyne; Qoryoley; Shangani; Shibis; South Galkacyo; South Galkaio; Waberi; Wadajir; Wardegley; Yaqshid</t>
+  </si>
+  <si>
+    <t>Data type: Infographic</t>
+  </si>
+  <si>
+    <t>Aadan Yabaal (Aden Yabaal); Afgooye; Afmadow; Baardheere; Badhaadhe; Balcad; Bandarbeyla; Baraawe; Baydhaba (Baidoa); Belet Weyne; Belet Xaawo; Berbera; Boorama (Borama); Bossaso; Bualle; Bulo Burte; Burco (Burao); Burtinle; Buuhoodle; Buur Hakaba (Burhakaba); Cabudwaaq; Cadale; Cadaado; Caluula; Caynabo; Ceel Afweyn; Ceel Barde; Ceel Buur; Ceel Dheer; Ceel Waaq; Ceerigaabo; Diinsoor; Doolow; Dhuusamarreeb; Eyl; Gaalkacyo; Galdogob; Garbahaarey; Garowe; Gebiley; Hargeysa; Hobyo; Iskushuban; Jalalaqsi; Jamaame; Jariiban; Jilib; Jowhar; Kismaayo (Kismayo); Kurtunwaarey; Laas Caanood; Laasqoray; Lughaye; Luuq; Mahaday; Marka; Oodweyne; Qandala; Qardho; Qoryooley; Rab Dhuure; Saakow; Sablaale; Taleex; Tiyeeglow (Tijieglo); Waajid; Wanla Weyn; Xarardheere; Xudur; Xudun; Zeylac</t>
+  </si>
+  <si>
+    <t>Afgooye; Afmadow; Baardheere; Badhaadhe; Baki; Bandarbeyla; Baraawe; Baydhaba; Belet Weyne; Belet Xaawo; Berbera; Borama; Bualle; Buhoodle; Bulo Burte; Burco; Burtinle; Buur Hakaba; Cabudwaaq; Cadaado; Caluula; Carmo; Ceel Afweyn; Ceel Barde; Ceel Waaq; Ceerigaabo; Dhahar; Dinsoor; Dollow; Eyl; Gaalkacyo; Garbahaarey; Gebiley; Hargeisa; Hobyo; Iskushuban; Jowhar; Kismaayo; Kurtunwaarey; Laas Canood; Laasqoray; Lughaye; Luuq; Marka; Mataban; Owdweyne; Qandala; Qansadheere; Qardho; Qoryooley; Rab Dhuure; Saakow; Sablaale; Sheikh; Taleex; Tayeeglow; Waajid; Wanla Weyne; Xudur; Xudun; Zeylac</t>
+  </si>
+  <si>
+    <t>Data type: News and press releases</t>
+  </si>
+  <si>
+    <t>Banadir, Puntland, South-West, Jubaland, and Hirshabelle</t>
+  </si>
+  <si>
+    <t>Baidoa (Baydhabo); Dhusamareeb; Gaalkacyo; Garowe; Hargeisa; Jamaame (Jamame); Jowhar; Kismayo; Mogadishu,Beledweyne</t>
+  </si>
+  <si>
+    <t>report</t>
+  </si>
+  <si>
+    <t>Baidoa; Daynile; Dhuusamarreeb; Gaalkacyo; Garowe; Hobyo; Jariiban; Khada; Xarardheere</t>
+  </si>
+  <si>
+    <t>Abdiaziz; Bondhere; Dharkenley; Hamar Jajab; Hamar Weyne; Hodan; Howlwadaag; Huriwa (Heliwa); Karan; Shangani; Shibis; Waberi; Wadajir; Warta Nabada; Yaqshid</t>
+  </si>
+  <si>
+    <t>map</t>
+  </si>
+  <si>
+    <t>Cabudwaaq; Cadaado; Ceel Buur; Ceel Dheer; Dhuusamarreeb</t>
+  </si>
+  <si>
+    <t>Adan Yabaal; Belet Weyne; Bulo Burto; Cadale; Gaalkacyo; Hobyo; Jalalaqsi; Mahas; Mataban; Xarardheere</t>
+  </si>
+  <si>
+    <t>news and press release</t>
+  </si>
+  <si>
+    <t>Beledweyne; Bosaso; Garowe; Jowhar; Kismayo; Mogadishu</t>
+  </si>
+  <si>
+    <t>Baidoa; Dhusamareb; Hargeisa</t>
+  </si>
+  <si>
+    <t>Afgooye; Afmadow; Baardheere; Badhan; Baidoa; Balcad; Bandarbeyla; Belet Weyne; Belet Xaawo; Baki; Borama; Bossaso; Bu'aale; Bulo Burto; Burco; Burtinle; Buuhoodle; Cabudwaaq; Ceel Afweyn; Ceel Barde; Ceel Dheer; Daynile; Dhahar; Dhuusamarreeb; Diinsoor; Doolow; Galdogob; Gaalkacyo; Garowe; Hargeysa; Heliwa; Hobyo; Jamaame; Jariiban; Jowhar; Kaxda; Kismayo; Kurtunwaarey; Laas Caanood; Marka; Qansax Dheere; Qardho; Qoryooley; Saakow; Xudur; Xudun</t>
+  </si>
+  <si>
+    <t>Jilib; Lughaye</t>
+  </si>
+  <si>
+    <t>infographics</t>
+  </si>
+  <si>
+    <t>Baidoa; Balcad (Bal'ad); Badhan; Beledweyne; Bosaso; Bulo Burte (Buleburte); Burco; Cabudwaaq (Abudwak); Cadaado (Adado); Ceel Dheer (El-dher); Dhuusamarreeb (Dhusamareb); Gaalkacyo (Galkayo); Galdogob (Goldogob); Hargeisa; Jariiban (Jarriban); Jowhar; Karan; Kismayo; Qoryooley (Torotorow); Xarardheere</t>
+  </si>
+  <si>
+    <t>Aden Yabal (Aden Yabal / Galad / Runingod); Adado; Afmadow; Baidoa; Bardera; Bulo Burti; Burdubo; Danyile; Dinsor (Dinsor district); El Bur; El Waq; Galhareri; Galkayu North; Galkayu South; Hagar; Heliwa; Hobyo; Hodan; Jilib East; Jowhar; Kismayu (Kismayo); Las Anod; Mahas; Qanaah Dere (Qansax Dheere); Salagle; Waberi; Yaqshid</t>
+  </si>
+  <si>
+    <t>Abdul Aziz; Adale; Afgoi; Alula; Awdheegle; Aynabo; Badhadhe; Badhan; Baki; Balad; Balanbale; Baligubadle; Bargaal; Bayla (Bender Bayla); Belet Hawa; Belet Weyne; Berbera; Berdale; Bondere; Borama; Bossaso; Brava; Buhodle; Buaale; Burhakaba; Burtinle; Caluula; Canyelo; Ceel Barde (El Barde); Ceel Dhere (El Dhere); Dangoroyo; Dharkenly; Dolo; Dusamreb; El Afweyn; Elgaras; Erigavo; Eyl; Gabiley; Gardo; Garbaharey; Garowe; Gedwein; Goldogob; Guriel; Hafun; Hamar Jabjab; Hamar Weyn; Haradhere; Hargeisa; Hawal Wadag; Hudun; Iskushuban; Jalalaqsi; Jamaame East; Jamaame West; Jilib West; Kahda; Karan; Kurtunwaarey; Luuq; Lughaya; Madina; Mahaday; Marka; Mataban; Odwayne; Qandala; Qoryoley; Rabdure; Raga Elle; Rako; Sablale; Sakow; Sheikh; Taleh; Tiyeglo; Ufeyn; Waciya; Wajid; Wanleweyne; Wardegly; Warsheikh; Zeila</t>
+  </si>
+  <si>
+    <t>Adan Yabal; Afgooye; Afmadow; Baardheere (Bardheere); Badhaadhe; Baraawe; Baydhaba; Beletweyne; Bondhere; Bossaso; Bulo Burto; Burco; Buur Hakaba; Cabudwaaq; Cadale; Cadaado; Caluula; Caynabo; Ceel Afweyn; Ceel Barde (Celbarde); Ceel Buur; Ceel Dheer; Ceel Waaq; Ceerigaabo; Dayniile; Dharkenley; Dhuusamarreeb; Diinsoor; Doloow; Galkayo; Galdogob; Garowe; Hamar Jajab; Heliwa; Hobyo; Hodan; Iskushuban; Jalalaqsi; Jamaame; Jowhar; Kismaayo; Laas Caanood; Laasqoray; Luuq; Marka; Owdeweyne; Qandala; Qansax Dheere; Qoryooley; Rabdhuree; Shangani; Shibis; Talex; Waajid; Wadajir; Wanla Weyn; Wardhigley; Xarardheere; Xuduur (Xudun/Xuduur); Yaaqshid</t>
+  </si>
+  <si>
+    <t>Awdheegle; Baki; Balanbale; Baligubadle; Bandarbeyla; Berbera; Berdale; Borama; Brava; Buhoodle; Burdubo; Burtinle; Garbahaarey; Hagar; Hargeysa; Jilib; Kurtunwaarey; Lughaye; Mahaday; Mataban; Qardho; Raga Elle; Saakow; Sablaale; Salagle; Sheikh; Tayeeglow; Warsheikh; Zeila</t>
+  </si>
+  <si>
+    <t>Afgooye; Afmadow; Baardheere; Baidoa; Balcad; Belet Weyne; Dayniile; Gaalkacyo; Garoowe; Hodan; Jamaame; Jowhar; Kahda; Kismaayo; Luuq</t>
+  </si>
+  <si>
+    <t>Burco; Buuhoodle; Owdweyne; Sheikh</t>
+  </si>
+  <si>
+    <t>Berbera; Caynabo; Ceel Afweyn; Ceerigaabo; Gebiley; Hargeysa; Laas Caanood; Salahley; Xudun</t>
+  </si>
+  <si>
+    <t>Adado; Adan Yabaal; Baidoa; Bardheere; Beletweyne; Bosasso; Burco (Burao); Ceel Barde (Elberde); Dhuusamarreeb (Dhusamareb); Doolow (Dolow); Gaalkacyo (Galkacyo); Garowe; Hargeisa; Kismayo (Kismayu); Mogadishu (Banadir); Qoryooley</t>
+  </si>
+  <si>
+    <t>Baidoa; Balcad (Balad / Buurfuule); Badhan; Bardera; Beletweyne; Buleburte; Burco (Burao / Kalbare / Dhoqoshey / Bali-Hajin); Buurdhubo; Cabudwaaq (Abudwak); Cadaado (Cadado / Barleef); Ceel Dheer (El-dher / El-Ma'an); Daynile; Dhuusamarreeb (Dhusamareb / Guriel); Dollow; Gaalkacyo (Galkayo); Garadag; Huriwa; Jalalaqsi; Jowhar; Kismayo; Mahas; Xudun (Hudun</t>
+  </si>
+  <si>
+    <t>assesment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kismayo, Jamaame </t>
+  </si>
+  <si>
+    <t>Mataban, Afmadow &amp; Badhaadhe,Mogadishu</t>
+  </si>
+  <si>
+    <t>meeting minute</t>
+  </si>
+  <si>
+    <t>Ceel Buur (Elbur); Ceel Dheer (Eldheer); Gaalkacyo (Galkio); Galcad; Hobyo; Jariiban (Jariban); Xarardheere (Haradhere)</t>
+  </si>
+  <si>
+    <t>Elgaras</t>
+  </si>
+  <si>
+    <t>Adado; Aden Yabal; Afmadow; Badhadhe; Baidoa; Bardera; Beletweyne; Brava; Bulo Burti; Burdubo; Danyile; Dhuusamarreeb (Dhusamreb); El Waq; Galhareri; Galkayu North; Galkayu South; Hagar; Heliwa; Hobyo; Hodan; Jilib East; Jowhar; Karan; Kismayu (Kismayo); Las Anod; Mahas; Qansax Dheere (Qanaah Dere); Salagle; Yaqshid</t>
+  </si>
+  <si>
+    <t>Abdul Aziz; Adale; Afgoi; Alula; Awdheegle; Aynabo; Baki; Balad; Balanbale; Baligubadle; Bargaal; Bayla (Bender Bayla); Belet Hawa; Berbera; Berdale; Bondere; Borama; Bossaso; Buaale; Buhodle; Burhakaba; Burtinle; Caluula; Ceel Barde (El Barde); Ceel Dhere (El Dhere); Dangoroyo; Dharkenly; Dolo; El Afweyn; El Bur (Elbur); Elgaras; Erigavo; Eyl; Gabiley; Garbaharey; Gardo; Garowe; Goldogob; Guriel; Hafun; Hamar Jabjab; Hamar Weyn; Haradhere; Hargeisa; Hawal Wadag; Hudun; Iskushuban; Jalalaqsi; Jamaame East; Jamaame West; Jilib West; Kahda; Kurtunwaarey; Lughaya; Luuq; Madina; Mahaday; Marka; Mataban; Odwayne; Qandala; Qoryoley; Rabdure; Raga Elle; Rako; Runingod; Sablale; Sakow; Sheikh; Taleh; Tiyeglo; Ufeyn; Waciya; Wajid; Wanleweyne; Wardegly; Warsheikh; Zeila</t>
+  </si>
+  <si>
+    <t>Cadaado (Adado); Gaalkacyo (Galkayo); Hobyo; Xarardheere (Harardheere)</t>
+  </si>
+  <si>
+    <t>Baidoa; Balcad; Banadir (Mogadishu); Buuhoodle; Jowhar; Kismayo; Laas Caanood; Luuq</t>
+  </si>
+  <si>
+    <t>Gaalkacyo (Gaalkacye); Hobyo; Waajid; Xudur</t>
+  </si>
+  <si>
+    <t>Abdul Aziz; Afgoye; Badhan; Baidoa; Balad (Hawadley Village); Banadir; Barawe; Beletweyn; Belethawo; Bondere; Borama; Bosaso; Bulo Burte; Burao; Burhakabe; Danyile; Dhahar; Dharkenly; Eigavo (Erigavo); Gabiley; Gardo; Garowe; Hamar jajab; Hamar weyn; Hargeisa; Hawl Wadag; Heliwa; Hodan; Jalalaqso; Jowhar; Kahda; Karan; Kismayo; Kuntunwarey (Kurtunwaarey); Lasqoray; Mahaday; Merka; Owdweyne; Qardho; Qoryoley; Shangani; Shibis; South Galkacyo; Waberi; Wadajir; Wardegley; Yaqshid</t>
+  </si>
+  <si>
+    <t>Adan Yabaal (Aden Yabal); Afgoi; Alula; Awdheegle; Aynabo; Badhadhe; Baki; Balanbale; Baligubadle; Bargaal; Bayla; Belet Hawa; Berbera; Berdale; Brava; Buhodle; Buur Hakaba; Buurdhubo; Cabudwaaq; Cadale; Caluula; Canyelo; Ceel Afweyn; Ceel Barde; Ceel Buur; Ceel Dhere; Ceel Waaq; Dangoroyo; Dhuusamarreeb; Diinsoor; Doolow; El Bur; Galad; Galdogob; Garbaharey; Gedwein; Goldogob; Guriel; Hafun; Hagar; Haradhere; Hobyo; Hudun; Iskushuban; Jamaame; Jilib; Las Anod; Luuq; Lughaye; Mahas; Mataban; Odwayne; Qandala; Qansax Dheere; Rabdure; Raga Elle; Rako; Runingod; Saakow; Sablaale; Salagle; Sheikh; Taleh; Tiyeglo; Ufeyn; Waajid; Wanlaweyn; Warsheikh; Xudur; Zeil</t>
+  </si>
+  <si>
+    <t>Abdiaziz; Afmadow; Baidoa (Baydhaba); Berbera; Borama; Cadaado; Ceel Waaq; Daynile (Dayniile); Diinsoor; Doolow; Garbahaarey; Garowe; Hargeysa; Jamaame; Jariiban; Kaxda (Kahda); Kismayo (Kismaayo / Qamqam); Laas Caanood; Luuq; Marka; Qoryooley; Waaberi (Wadajir-Waaberi); Wadajir; Wanla Weyn; Xudun</t>
+  </si>
+  <si>
+    <t>Report</t>
   </si>
 </sst>
 </file>
@@ -4049,7 +4163,7 @@
         <v>58</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="J4" s="9" t="s">
         <v>815</v>
@@ -4058,7 +4172,7 @@
         <v>45</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
@@ -4094,7 +4208,7 @@
         <v>45</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="178.5" x14ac:dyDescent="0.45">
@@ -4170,7 +4284,7 @@
         <v>46</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="114.75" x14ac:dyDescent="0.45">
@@ -4208,7 +4322,7 @@
         <v>46</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="357" x14ac:dyDescent="0.45">
@@ -4246,7 +4360,7 @@
         <v>46</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="89.25" x14ac:dyDescent="0.45">
@@ -4276,13 +4390,13 @@
         <v>815</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>46</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="178.5" x14ac:dyDescent="0.45">
@@ -4311,7 +4425,7 @@
         <v>84</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>815</v>
@@ -4320,7 +4434,7 @@
         <v>45</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="165.75" x14ac:dyDescent="0.45">
@@ -4348,17 +4462,17 @@
       <c r="H12" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="I12" s="17" t="s">
         <v>818</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>46</v>
       </c>
       <c r="L12" s="14" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="280.5" x14ac:dyDescent="0.45">
@@ -4387,7 +4501,7 @@
         <v>92</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="J13" s="14" t="s">
         <v>46</v>
@@ -4396,7 +4510,7 @@
         <v>46</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="25.5" x14ac:dyDescent="0.45">
@@ -4470,7 +4584,7 @@
         <v>45</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="216.75" x14ac:dyDescent="0.45">
@@ -4508,7 +4622,7 @@
         <v>46</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="178.5" x14ac:dyDescent="0.45">
@@ -4537,7 +4651,7 @@
         <v>108</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="J17" s="15" t="s">
         <v>815</v>
@@ -4575,19 +4689,19 @@
         <v>112</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>815</v>
+        <v>906</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="K18" s="9" t="s">
         <v>46</v>
       </c>
       <c r="L18" s="14" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="395.25" x14ac:dyDescent="0.45">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="409.5" x14ac:dyDescent="0.45">
       <c r="A19" s="7">
         <v>17</v>
       </c>
@@ -4610,11 +4724,11 @@
         <v>46</v>
       </c>
       <c r="H19" s="8"/>
-      <c r="I19" s="9" t="s">
+      <c r="I19" s="14" t="s">
+        <v>828</v>
+      </c>
+      <c r="J19" s="14" t="s">
         <v>815</v>
-      </c>
-      <c r="J19" s="14" t="s">
-        <v>830</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>46</v>
@@ -4623,7 +4737,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="38.25" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:12" ht="51" x14ac:dyDescent="0.45">
       <c r="A20" s="7">
         <v>18</v>
       </c>
@@ -4646,11 +4760,11 @@
         <v>46</v>
       </c>
       <c r="H20" s="8"/>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="14" t="s">
+        <v>905</v>
+      </c>
+      <c r="J20" s="14" t="s">
         <v>815</v>
-      </c>
-      <c r="J20" s="14" t="s">
-        <v>831</v>
       </c>
       <c r="K20" s="9" t="s">
         <v>46</v>
@@ -4685,7 +4799,7 @@
         <v>122</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="J21" s="9" t="s">
         <v>815</v>
@@ -4694,7 +4808,7 @@
         <v>46</v>
       </c>
       <c r="L21" s="14" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="140.25" x14ac:dyDescent="0.45">
@@ -4732,7 +4846,7 @@
         <v>46</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="89.25" x14ac:dyDescent="0.45">
@@ -4770,7 +4884,7 @@
         <v>46</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="38.25" x14ac:dyDescent="0.45">
@@ -4799,16 +4913,16 @@
         <v>134</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="K24" s="9" t="s">
         <v>46</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="63.75" x14ac:dyDescent="0.45">
@@ -4846,7 +4960,7 @@
         <v>45</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="153" x14ac:dyDescent="0.45">
@@ -4879,7 +4993,7 @@
       <c r="K26" s="9"/>
       <c r="L26" s="9"/>
     </row>
-    <row r="27" spans="1:12" ht="191.25" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:12" ht="331.5" x14ac:dyDescent="0.45">
       <c r="A27" s="7">
         <v>25</v>
       </c>
@@ -4905,16 +5019,16 @@
         <v>145</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>852</v>
+        <v>907</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>853</v>
+        <v>908</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>46</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="153" x14ac:dyDescent="0.45">
@@ -4943,10 +5057,10 @@
         <v>149</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="K28" s="9" t="s">
         <v>45</v>
@@ -4988,7 +5102,7 @@
         <v>46</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="204" x14ac:dyDescent="0.45">
@@ -5017,16 +5131,16 @@
         <v>157</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="K30" s="15" t="s">
         <v>46</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="102" x14ac:dyDescent="0.45">
@@ -5064,7 +5178,7 @@
         <v>46</v>
       </c>
       <c r="L31" s="9" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="178.5" x14ac:dyDescent="0.45">
@@ -5174,7 +5288,7 @@
         <v>45</v>
       </c>
       <c r="L34" s="9" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="140.25" x14ac:dyDescent="0.45">
@@ -5203,7 +5317,7 @@
         <v>177</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="J35" s="14" t="s">
         <v>815</v>
@@ -5211,8 +5325,8 @@
       <c r="K35" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="L35" s="17" t="s">
-        <v>823</v>
+      <c r="L35" s="14" t="s">
+        <v>874</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="89.25" x14ac:dyDescent="0.45">
@@ -5241,17 +5355,15 @@
         <v>181</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="K36" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="L36" s="17" t="s">
-        <v>823</v>
-      </c>
+      <c r="L36" s="17"/>
     </row>
     <row r="37" spans="1:12" ht="76.5" x14ac:dyDescent="0.45">
       <c r="A37" s="7">
@@ -5277,17 +5389,15 @@
       </c>
       <c r="H37" s="8"/>
       <c r="I37" s="14" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="K37" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="L37" s="17" t="s">
-        <v>823</v>
-      </c>
+      <c r="L37" s="17"/>
     </row>
     <row r="38" spans="1:12" ht="25.5" x14ac:dyDescent="0.45">
       <c r="A38" s="7">
@@ -5459,10 +5569,10 @@
         <v>202</v>
       </c>
       <c r="I42" s="14" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="K42" s="15" t="s">
         <v>46</v>
@@ -5471,7 +5581,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="140.25" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:12" ht="165.75" x14ac:dyDescent="0.45">
       <c r="A43" s="7">
         <v>41</v>
       </c>
@@ -5496,17 +5606,17 @@
       <c r="H43" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="I43" s="17" t="s">
-        <v>826</v>
-      </c>
-      <c r="J43" s="17" t="s">
-        <v>827</v>
+      <c r="I43" s="14" t="s">
+        <v>909</v>
+      </c>
+      <c r="J43" s="14" t="s">
+        <v>683</v>
       </c>
       <c r="K43" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="L43" s="17" t="s">
-        <v>823</v>
+      <c r="L43" s="14" t="s">
+        <v>910</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="25.5" x14ac:dyDescent="0.45">
@@ -5540,7 +5650,7 @@
       </c>
       <c r="K44" s="9"/>
       <c r="L44" s="14" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="255" x14ac:dyDescent="0.45">
@@ -5569,15 +5679,17 @@
         <v>211</v>
       </c>
       <c r="I45" s="14" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="J45" s="14" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="K45" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L45" s="9"/>
+      <c r="L45" s="9" t="s">
+        <v>874</v>
+      </c>
     </row>
     <row r="46" spans="1:12" ht="25.5" x14ac:dyDescent="0.45">
       <c r="A46" s="7">
@@ -5613,9 +5725,7 @@
       <c r="K46" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="L46" s="9" t="s">
-        <v>45</v>
-      </c>
+      <c r="L46" s="9"/>
     </row>
     <row r="47" spans="1:12" ht="191.25" x14ac:dyDescent="0.45">
       <c r="A47" s="7">
@@ -5643,19 +5753,19 @@
         <v>218</v>
       </c>
       <c r="I47" s="14" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="K47" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L47" s="17" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="102" x14ac:dyDescent="0.45">
+      <c r="L47" s="14" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="409.5" x14ac:dyDescent="0.45">
       <c r="A48" s="7">
         <v>46</v>
       </c>
@@ -5680,12 +5790,18 @@
       <c r="H48" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="I48" s="9"/>
-      <c r="J48" s="14"/>
+      <c r="I48" s="14" t="s">
+        <v>869</v>
+      </c>
+      <c r="J48" s="14" t="s">
+        <v>815</v>
+      </c>
       <c r="K48" s="9"/>
-      <c r="L48" s="17"/>
-    </row>
-    <row r="49" spans="1:12" ht="178.5" x14ac:dyDescent="0.45">
+      <c r="L48" s="14" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="318.75" x14ac:dyDescent="0.45">
       <c r="A49" s="7">
         <v>47</v>
       </c>
@@ -5710,10 +5826,16 @@
       <c r="H49" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="I49" s="9"/>
-      <c r="J49" s="9"/>
+      <c r="I49" s="14" t="s">
+        <v>870</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K49" s="9"/>
-      <c r="L49" s="9"/>
+      <c r="L49" s="9" t="s">
+        <v>829</v>
+      </c>
     </row>
     <row r="50" spans="1:12" ht="280.5" x14ac:dyDescent="0.45">
       <c r="A50" s="7">
@@ -5728,7 +5850,7 @@
       <c r="D50" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="E50" s="7" t="s">
+      <c r="E50" s="13" t="s">
         <v>229</v>
       </c>
       <c r="F50" s="7" t="s">
@@ -5740,10 +5862,16 @@
       <c r="H50" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="I50" s="9"/>
-      <c r="J50" s="9"/>
+      <c r="I50" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="J50" s="9" t="s">
+        <v>616</v>
+      </c>
       <c r="K50" s="9"/>
-      <c r="L50" s="9"/>
+      <c r="L50" s="9" t="s">
+        <v>871</v>
+      </c>
     </row>
     <row r="51" spans="1:12" ht="153" x14ac:dyDescent="0.45">
       <c r="A51" s="7">
@@ -5758,7 +5886,7 @@
       <c r="D51" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="E51" s="7" t="s">
+      <c r="E51" s="13" t="s">
         <v>233</v>
       </c>
       <c r="F51" s="7" t="s">
@@ -5770,10 +5898,16 @@
       <c r="H51" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="I51" s="9"/>
-      <c r="J51" s="9"/>
+      <c r="I51" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="J51" s="14" t="s">
+        <v>872</v>
+      </c>
       <c r="K51" s="9"/>
-      <c r="L51" s="9"/>
+      <c r="L51" s="9" t="s">
+        <v>871</v>
+      </c>
     </row>
     <row r="52" spans="1:12" ht="204" x14ac:dyDescent="0.45">
       <c r="A52" s="7">
@@ -5788,7 +5922,7 @@
       <c r="D52" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="E52" s="7" t="s">
+      <c r="E52" s="13" t="s">
         <v>237</v>
       </c>
       <c r="F52" s="7" t="s">
@@ -5800,10 +5934,16 @@
       <c r="H52" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="I52" s="9"/>
-      <c r="J52" s="9"/>
+      <c r="I52" s="9" t="s">
+        <v>810</v>
+      </c>
+      <c r="J52" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K52" s="9"/>
-      <c r="L52" s="9"/>
+      <c r="L52" s="9" t="s">
+        <v>846</v>
+      </c>
     </row>
     <row r="53" spans="1:12" ht="76.5" x14ac:dyDescent="0.45">
       <c r="A53" s="7">
@@ -5818,7 +5958,7 @@
       <c r="D53" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="E53" s="7" t="s">
+      <c r="E53" s="13" t="s">
         <v>241</v>
       </c>
       <c r="F53" s="7" t="s">
@@ -5830,10 +5970,16 @@
       <c r="H53" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="I53" s="9"/>
-      <c r="J53" s="9"/>
+      <c r="I53" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="J53" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K53" s="9"/>
-      <c r="L53" s="9"/>
+      <c r="L53" s="9" t="s">
+        <v>820</v>
+      </c>
     </row>
     <row r="54" spans="1:12" ht="114.75" x14ac:dyDescent="0.45">
       <c r="A54" s="7">
@@ -5848,7 +5994,7 @@
       <c r="D54" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="E54" s="7" t="s">
+      <c r="E54" s="13" t="s">
         <v>245</v>
       </c>
       <c r="F54" s="7" t="s">
@@ -5860,10 +6006,16 @@
       <c r="H54" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="I54" s="9"/>
-      <c r="J54" s="9"/>
+      <c r="I54" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="J54" s="14" t="s">
+        <v>873</v>
+      </c>
       <c r="K54" s="9"/>
-      <c r="L54" s="9"/>
+      <c r="L54" s="9" t="s">
+        <v>874</v>
+      </c>
     </row>
     <row r="55" spans="1:12" ht="89.25" x14ac:dyDescent="0.45">
       <c r="A55" s="7">
@@ -5878,7 +6030,7 @@
       <c r="D55" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="E55" s="7" t="s">
+      <c r="E55" s="13" t="s">
         <v>248</v>
       </c>
       <c r="F55" s="7" t="s">
@@ -5890,10 +6042,16 @@
       <c r="H55" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="I55" s="9"/>
-      <c r="J55" s="9"/>
+      <c r="I55" s="14" t="s">
+        <v>875</v>
+      </c>
+      <c r="J55" s="14" t="s">
+        <v>876</v>
+      </c>
       <c r="K55" s="9"/>
-      <c r="L55" s="9"/>
+      <c r="L55" s="9" t="s">
+        <v>820</v>
+      </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A56" s="7">
@@ -5908,7 +6066,7 @@
       <c r="D56" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="E56" s="7" t="s">
+      <c r="E56" s="13" t="s">
         <v>252</v>
       </c>
       <c r="F56" s="7" t="s">
@@ -5918,12 +6076,18 @@
         <v>46</v>
       </c>
       <c r="H56" s="8"/>
-      <c r="I56" s="9"/>
-      <c r="J56" s="9"/>
+      <c r="I56" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="J56" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K56" s="9"/>
-      <c r="L56" s="9"/>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="L56" s="9" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="51" x14ac:dyDescent="0.45">
       <c r="A57" s="7">
         <v>55</v>
       </c>
@@ -5936,7 +6100,7 @@
       <c r="D57" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="E57" s="7" t="s">
+      <c r="E57" s="13" t="s">
         <v>255</v>
       </c>
       <c r="F57" s="7" t="s">
@@ -5948,10 +6112,16 @@
       <c r="H57" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="I57" s="9"/>
-      <c r="J57" s="9"/>
+      <c r="I57" s="14" t="s">
+        <v>878</v>
+      </c>
+      <c r="J57" s="14" t="s">
+        <v>879</v>
+      </c>
       <c r="K57" s="9"/>
-      <c r="L57" s="9"/>
+      <c r="L57" s="9" t="s">
+        <v>877</v>
+      </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A58" s="7">
@@ -5966,7 +6136,7 @@
       <c r="D58" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="E58" s="7" t="s">
+      <c r="E58" s="13" t="s">
         <v>258</v>
       </c>
       <c r="F58" s="7" t="s">
@@ -5976,8 +6146,12 @@
         <v>46</v>
       </c>
       <c r="H58" s="8"/>
-      <c r="I58" s="9"/>
-      <c r="J58" s="9"/>
+      <c r="I58" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="J58" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K58" s="9"/>
       <c r="L58" s="9"/>
     </row>
@@ -5994,7 +6168,7 @@
       <c r="D59" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="E59" s="7" t="s">
+      <c r="E59" s="13" t="s">
         <v>260</v>
       </c>
       <c r="F59" s="7" t="s">
@@ -6006,10 +6180,16 @@
       <c r="H59" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="I59" s="9"/>
-      <c r="J59" s="9"/>
+      <c r="I59" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="J59" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K59" s="9"/>
-      <c r="L59" s="9"/>
+      <c r="L59" s="9" t="s">
+        <v>880</v>
+      </c>
     </row>
     <row r="60" spans="1:12" ht="229.5" x14ac:dyDescent="0.45">
       <c r="A60" s="7">
@@ -6024,7 +6204,7 @@
       <c r="D60" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="E60" s="7" t="s">
+      <c r="E60" s="13" t="s">
         <v>264</v>
       </c>
       <c r="F60" s="7" t="s">
@@ -6036,12 +6216,18 @@
       <c r="H60" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="I60" s="9"/>
-      <c r="J60" s="9"/>
+      <c r="I60" s="14" t="s">
+        <v>881</v>
+      </c>
+      <c r="J60" s="9" t="s">
+        <v>882</v>
+      </c>
       <c r="K60" s="9"/>
-      <c r="L60" s="9"/>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="L60" s="9" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="242.25" x14ac:dyDescent="0.45">
       <c r="A61" s="7">
         <v>59</v>
       </c>
@@ -6054,7 +6240,7 @@
       <c r="D61" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="E61" s="7" t="s">
+      <c r="E61" s="13" t="s">
         <v>268</v>
       </c>
       <c r="F61" s="7" t="s">
@@ -6064,10 +6250,16 @@
         <v>46</v>
       </c>
       <c r="H61" s="8"/>
-      <c r="I61" s="9"/>
-      <c r="J61" s="9"/>
+      <c r="I61" s="14" t="s">
+        <v>883</v>
+      </c>
+      <c r="J61" s="9" t="s">
+        <v>884</v>
+      </c>
       <c r="K61" s="9"/>
-      <c r="L61" s="9"/>
+      <c r="L61" s="9" t="s">
+        <v>885</v>
+      </c>
     </row>
     <row r="62" spans="1:12" ht="242.25" x14ac:dyDescent="0.45">
       <c r="A62" s="7">
@@ -6082,7 +6274,7 @@
       <c r="D62" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E62" s="7" t="s">
+      <c r="E62" s="13" t="s">
         <v>271</v>
       </c>
       <c r="F62" s="7" t="s">
@@ -6094,10 +6286,16 @@
       <c r="H62" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="I62" s="9"/>
-      <c r="J62" s="9"/>
+      <c r="I62" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="J62" s="9" t="s">
+        <v>616</v>
+      </c>
       <c r="K62" s="9"/>
-      <c r="L62" s="9"/>
+      <c r="L62" s="9" t="s">
+        <v>880</v>
+      </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A63" s="7">
@@ -6112,7 +6310,7 @@
       <c r="D63" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="E63" s="7" t="s">
+      <c r="E63" s="13" t="s">
         <v>275</v>
       </c>
       <c r="F63" s="7" t="s">
@@ -6122,12 +6320,18 @@
         <v>46</v>
       </c>
       <c r="H63" s="8"/>
-      <c r="I63" s="9"/>
-      <c r="J63" s="9"/>
+      <c r="I63" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="J63" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K63" s="9"/>
-      <c r="L63" s="9"/>
-    </row>
-    <row r="64" spans="1:12" ht="165.75" x14ac:dyDescent="0.45">
+      <c r="L63" s="9" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="178.5" x14ac:dyDescent="0.45">
       <c r="A64" s="7">
         <v>62</v>
       </c>
@@ -6140,7 +6344,7 @@
       <c r="D64" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="E64" s="7" t="s">
+      <c r="E64" s="13" t="s">
         <v>278</v>
       </c>
       <c r="F64" s="7" t="s">
@@ -6152,10 +6356,16 @@
       <c r="H64" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="I64" s="9"/>
-      <c r="J64" s="9"/>
+      <c r="I64" s="14" t="s">
+        <v>886</v>
+      </c>
+      <c r="J64" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K64" s="9"/>
-      <c r="L64" s="9"/>
+      <c r="L64" s="9" t="s">
+        <v>874</v>
+      </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A65" s="7">
@@ -6170,7 +6380,7 @@
       <c r="D65" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="E65" s="7" t="s">
+      <c r="E65" s="13" t="s">
         <v>282</v>
       </c>
       <c r="F65" s="7" t="s">
@@ -6180,12 +6390,18 @@
         <v>46</v>
       </c>
       <c r="H65" s="8"/>
-      <c r="I65" s="9"/>
-      <c r="J65" s="9"/>
+      <c r="I65" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="J65" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K65" s="9"/>
-      <c r="L65" s="9"/>
-    </row>
-    <row r="66" spans="1:12" ht="102" x14ac:dyDescent="0.45">
+      <c r="L65" s="9" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="382.5" x14ac:dyDescent="0.45">
       <c r="A66" s="7">
         <v>64</v>
       </c>
@@ -6198,7 +6414,7 @@
       <c r="D66" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="E66" s="7" t="s">
+      <c r="E66" s="13" t="s">
         <v>285</v>
       </c>
       <c r="F66" s="7" t="s">
@@ -6210,10 +6426,16 @@
       <c r="H66" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="I66" s="9"/>
-      <c r="J66" s="9"/>
+      <c r="I66" s="14" t="s">
+        <v>887</v>
+      </c>
+      <c r="J66" s="14" t="s">
+        <v>888</v>
+      </c>
       <c r="K66" s="9"/>
-      <c r="L66" s="9"/>
+      <c r="L66" s="9" t="s">
+        <v>874</v>
+      </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A67" s="7">
@@ -6228,7 +6450,7 @@
       <c r="D67" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="E67" s="7" t="s">
+      <c r="E67" s="13" t="s">
         <v>288</v>
       </c>
       <c r="F67" s="7" t="s">
@@ -6238,10 +6460,16 @@
         <v>46</v>
       </c>
       <c r="H67" s="8"/>
-      <c r="I67" s="9"/>
-      <c r="J67" s="9"/>
+      <c r="I67" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="J67" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K67" s="9"/>
-      <c r="L67" s="9"/>
+      <c r="L67" s="9" t="s">
+        <v>885</v>
+      </c>
     </row>
     <row r="68" spans="1:12" ht="140.25" x14ac:dyDescent="0.45">
       <c r="A68" s="7">
@@ -6256,7 +6484,7 @@
       <c r="D68" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="E68" s="7" t="s">
+      <c r="E68" s="13" t="s">
         <v>290</v>
       </c>
       <c r="F68" s="7" t="s">
@@ -6268,12 +6496,18 @@
       <c r="H68" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="I68" s="9"/>
-      <c r="J68" s="9"/>
+      <c r="I68" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="J68" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K68" s="9"/>
-      <c r="L68" s="9"/>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="L68" s="9" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="344.25" x14ac:dyDescent="0.45">
       <c r="A69" s="7">
         <v>67</v>
       </c>
@@ -6286,7 +6520,7 @@
       <c r="D69" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="E69" s="7" t="s">
+      <c r="E69" s="13" t="s">
         <v>293</v>
       </c>
       <c r="F69" s="7" t="s">
@@ -6296,10 +6530,16 @@
         <v>46</v>
       </c>
       <c r="H69" s="8"/>
-      <c r="I69" s="9"/>
-      <c r="J69" s="9"/>
+      <c r="I69" s="14" t="s">
+        <v>889</v>
+      </c>
+      <c r="J69" s="14" t="s">
+        <v>890</v>
+      </c>
       <c r="K69" s="9"/>
-      <c r="L69" s="9"/>
+      <c r="L69" s="9" t="s">
+        <v>885</v>
+      </c>
     </row>
     <row r="70" spans="1:12" ht="114.75" x14ac:dyDescent="0.45">
       <c r="A70" s="7">
@@ -6314,7 +6554,7 @@
       <c r="D70" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="E70" s="7" t="s">
+      <c r="E70" s="13" t="s">
         <v>296</v>
       </c>
       <c r="F70" s="7" t="s">
@@ -6326,12 +6566,18 @@
       <c r="H70" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="I70" s="9"/>
-      <c r="J70" s="9"/>
+      <c r="I70" s="14" t="s">
+        <v>891</v>
+      </c>
+      <c r="J70" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K70" s="9"/>
-      <c r="L70" s="9"/>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="L70" s="9" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="51" x14ac:dyDescent="0.45">
       <c r="A71" s="7">
         <v>69</v>
       </c>
@@ -6344,7 +6590,7 @@
       <c r="D71" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="E71" s="7" t="s">
+      <c r="E71" s="13" t="s">
         <v>300</v>
       </c>
       <c r="F71" s="7" t="s">
@@ -6354,10 +6600,16 @@
         <v>46</v>
       </c>
       <c r="H71" s="8"/>
-      <c r="I71" s="9"/>
-      <c r="J71" s="9"/>
+      <c r="I71" s="14" t="s">
+        <v>892</v>
+      </c>
+      <c r="J71" s="14" t="s">
+        <v>893</v>
+      </c>
       <c r="K71" s="9"/>
-      <c r="L71" s="9"/>
+      <c r="L71" s="9" t="s">
+        <v>877</v>
+      </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A72" s="7">
@@ -6372,7 +6624,7 @@
       <c r="D72" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="E72" s="7" t="s">
+      <c r="E72" s="13" t="s">
         <v>302</v>
       </c>
       <c r="F72" s="7" t="s">
@@ -6382,12 +6634,18 @@
         <v>46</v>
       </c>
       <c r="H72" s="8"/>
-      <c r="I72" s="9"/>
-      <c r="J72" s="9"/>
+      <c r="I72" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="J72" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K72" s="9"/>
-      <c r="L72" s="9"/>
-    </row>
-    <row r="73" spans="1:12" ht="89.25" x14ac:dyDescent="0.45">
+      <c r="L72" s="9" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="140.25" x14ac:dyDescent="0.45">
       <c r="A73" s="7">
         <v>71</v>
       </c>
@@ -6400,7 +6658,7 @@
       <c r="D73" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E73" s="7" t="s">
+      <c r="E73" s="13" t="s">
         <v>305</v>
       </c>
       <c r="F73" s="7" t="s">
@@ -6412,12 +6670,18 @@
       <c r="H73" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="I73" s="9"/>
-      <c r="J73" s="9"/>
+      <c r="I73" s="14" t="s">
+        <v>894</v>
+      </c>
+      <c r="J73" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K73" s="9"/>
-      <c r="L73" s="9"/>
-    </row>
-    <row r="74" spans="1:12" ht="140.25" x14ac:dyDescent="0.45">
+      <c r="L73" s="9" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="191.25" x14ac:dyDescent="0.45">
       <c r="A74" s="7">
         <v>72</v>
       </c>
@@ -6430,7 +6694,7 @@
       <c r="D74" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="E74" s="7" t="s">
+      <c r="E74" s="13" t="s">
         <v>309</v>
       </c>
       <c r="F74" s="7" t="s">
@@ -6442,10 +6706,16 @@
       <c r="H74" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="I74" s="9"/>
-      <c r="J74" s="9"/>
+      <c r="I74" s="14" t="s">
+        <v>895</v>
+      </c>
+      <c r="J74" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K74" s="9"/>
-      <c r="L74" s="9"/>
+      <c r="L74" s="9" t="s">
+        <v>874</v>
+      </c>
     </row>
     <row r="75" spans="1:12" ht="216.75" x14ac:dyDescent="0.45">
       <c r="A75" s="7">
@@ -6460,7 +6730,7 @@
       <c r="D75" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="E75" s="7" t="s">
+      <c r="E75" s="13" t="s">
         <v>313</v>
       </c>
       <c r="F75" s="7" t="s">
@@ -6472,10 +6742,16 @@
       <c r="H75" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="I75" s="9"/>
-      <c r="J75" s="9"/>
+      <c r="I75" s="9" t="s">
+        <v>897</v>
+      </c>
+      <c r="J75" s="14" t="s">
+        <v>898</v>
+      </c>
       <c r="K75" s="9"/>
-      <c r="L75" s="9"/>
+      <c r="L75" s="9" t="s">
+        <v>896</v>
+      </c>
     </row>
     <row r="76" spans="1:12" ht="204" x14ac:dyDescent="0.45">
       <c r="A76" s="7">
@@ -6490,7 +6766,7 @@
       <c r="D76" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="E76" s="7" t="s">
+      <c r="E76" s="13" t="s">
         <v>317</v>
       </c>
       <c r="F76" s="7" t="s">
@@ -6502,10 +6778,16 @@
       <c r="H76" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="I76" s="9"/>
-      <c r="J76" s="9"/>
+      <c r="I76" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="J76" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K76" s="9"/>
-      <c r="L76" s="9"/>
+      <c r="L76" s="9" t="s">
+        <v>880</v>
+      </c>
     </row>
     <row r="77" spans="1:12" ht="140.25" x14ac:dyDescent="0.45">
       <c r="A77" s="7">
@@ -6520,7 +6802,7 @@
       <c r="D77" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="E77" s="7" t="s">
+      <c r="E77" s="13" t="s">
         <v>321</v>
       </c>
       <c r="F77" s="7" t="s">
@@ -6532,12 +6814,18 @@
       <c r="H77" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="I77" s="9"/>
-      <c r="J77" s="9"/>
+      <c r="I77" s="14" t="s">
+        <v>900</v>
+      </c>
+      <c r="J77" s="9" t="s">
+        <v>901</v>
+      </c>
       <c r="K77" s="9"/>
-      <c r="L77" s="9"/>
-    </row>
-    <row r="78" spans="1:12" ht="102" x14ac:dyDescent="0.45">
+      <c r="L77" s="9" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="357" x14ac:dyDescent="0.45">
       <c r="A78" s="7">
         <v>76</v>
       </c>
@@ -6550,7 +6838,7 @@
       <c r="D78" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="E78" s="7" t="s">
+      <c r="E78" s="13" t="s">
         <v>325</v>
       </c>
       <c r="F78" s="7" t="s">
@@ -6562,10 +6850,16 @@
       <c r="H78" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="I78" s="9"/>
-      <c r="J78" s="9"/>
+      <c r="I78" s="14" t="s">
+        <v>902</v>
+      </c>
+      <c r="J78" s="14" t="s">
+        <v>903</v>
+      </c>
       <c r="K78" s="9"/>
-      <c r="L78" s="9"/>
+      <c r="L78" s="9" t="s">
+        <v>874</v>
+      </c>
     </row>
     <row r="79" spans="1:12" ht="165.75" x14ac:dyDescent="0.45">
       <c r="A79" s="7">
@@ -6580,7 +6874,7 @@
       <c r="D79" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="E79" s="7" t="s">
+      <c r="E79" s="13" t="s">
         <v>329</v>
       </c>
       <c r="F79" s="7" t="s">
@@ -6592,10 +6886,16 @@
       <c r="H79" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="I79" s="9"/>
-      <c r="J79" s="9"/>
+      <c r="I79" s="14" t="s">
+        <v>904</v>
+      </c>
+      <c r="J79" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K79" s="9"/>
-      <c r="L79" s="9"/>
+      <c r="L79" s="9" t="s">
+        <v>874</v>
+      </c>
     </row>
     <row r="80" spans="1:12" ht="89.25" x14ac:dyDescent="0.45">
       <c r="A80" s="7">
@@ -6610,7 +6910,7 @@
       <c r="D80" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="E80" s="7" t="s">
+      <c r="E80" s="13" t="s">
         <v>333</v>
       </c>
       <c r="F80" s="7" t="s">
@@ -6622,10 +6922,16 @@
       <c r="H80" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="I80" s="9"/>
-      <c r="J80" s="9"/>
+      <c r="I80" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="J80" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K80" s="9"/>
-      <c r="L80" s="9"/>
+      <c r="L80" s="9" t="s">
+        <v>885</v>
+      </c>
     </row>
     <row r="81" spans="1:12" ht="25.5" x14ac:dyDescent="0.45">
       <c r="A81" s="7">
@@ -6640,7 +6946,7 @@
       <c r="D81" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="E81" s="7" t="s">
+      <c r="E81" s="13" t="s">
         <v>336</v>
       </c>
       <c r="F81" s="7" t="s">
@@ -6652,10 +6958,16 @@
       <c r="H81" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="I81" s="9"/>
-      <c r="J81" s="9"/>
+      <c r="I81" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="J81" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K81" s="9"/>
-      <c r="L81" s="9"/>
+      <c r="L81" s="9" t="s">
+        <v>877</v>
+      </c>
     </row>
     <row r="82" spans="1:12" ht="204" x14ac:dyDescent="0.45">
       <c r="A82" s="7">
@@ -8817,9 +9129,41 @@
     <hyperlink ref="E49" r:id="rId46" xr:uid="{1C8774A2-A9A1-4F43-98F6-C951B8423B16}"/>
     <hyperlink ref="E4" r:id="rId47" xr:uid="{E8146D32-CBAE-417B-AA12-BA90E9334704}"/>
     <hyperlink ref="E44" r:id="rId48" xr:uid="{2F1D026A-CF24-42C1-B8D0-B911D595C828}"/>
+    <hyperlink ref="E50" r:id="rId49" xr:uid="{CBEA990E-3760-41AA-976E-32461EACF251}"/>
+    <hyperlink ref="E51" r:id="rId50" xr:uid="{2A95B796-AFE1-4454-A10E-11C2643B0426}"/>
+    <hyperlink ref="E52" r:id="rId51" xr:uid="{56C84C87-C464-4F83-9AF2-C7B6DDC3C935}"/>
+    <hyperlink ref="E53" r:id="rId52" xr:uid="{7F09C477-C202-4B94-92EC-36EDBC6D9E27}"/>
+    <hyperlink ref="E54" r:id="rId53" xr:uid="{FD8CEE68-A9FD-4C5A-A628-B13980DF6DE7}"/>
+    <hyperlink ref="E55" r:id="rId54" xr:uid="{0A030746-C3B4-420C-81DA-4945CB82B84C}"/>
+    <hyperlink ref="E56" r:id="rId55" xr:uid="{CE28EC2B-75F6-4DBC-946E-6ECB03E548C0}"/>
+    <hyperlink ref="E57" r:id="rId56" xr:uid="{7FEC93AA-E64E-4472-9649-EA39B1C02F48}"/>
+    <hyperlink ref="E58" r:id="rId57" xr:uid="{E9777CCF-1C79-42FA-879F-F67F0968955D}"/>
+    <hyperlink ref="E59" r:id="rId58" xr:uid="{6BC495F2-D2D5-421E-9441-DFC89F0878BD}"/>
+    <hyperlink ref="E60" r:id="rId59" xr:uid="{2AB4E712-0C4F-4BF3-8E95-622CCA457C99}"/>
+    <hyperlink ref="E61" r:id="rId60" xr:uid="{D79AAE37-0CE4-4609-8362-F0C96E6BE97F}"/>
+    <hyperlink ref="E62" r:id="rId61" xr:uid="{0BDF392A-DDCB-42C0-AAA6-C07D9EB666DA}"/>
+    <hyperlink ref="E63" r:id="rId62" xr:uid="{F8DC553C-18EA-4338-8AED-65EF3448BB37}"/>
+    <hyperlink ref="E64" r:id="rId63" xr:uid="{5E6C98BF-B863-4E72-BF73-C93E2F5B5ACA}"/>
+    <hyperlink ref="E65" r:id="rId64" xr:uid="{5A007684-3A93-4E09-BF32-87C4D90920D5}"/>
+    <hyperlink ref="E66" r:id="rId65" xr:uid="{DC99492A-B459-483F-A6EA-4E9D0AB281BF}"/>
+    <hyperlink ref="E67" r:id="rId66" xr:uid="{BF0339BC-8F76-4158-BC62-089AAC1BF713}"/>
+    <hyperlink ref="E68" r:id="rId67" xr:uid="{B831444B-8F34-44C0-B7F5-4B21A3C18178}"/>
+    <hyperlink ref="E69" r:id="rId68" xr:uid="{D1ACEAAB-9EBA-4851-9837-4B3A64772FAE}"/>
+    <hyperlink ref="E70" r:id="rId69" xr:uid="{B75B6CCB-A4FD-4A19-9544-6E96E487D118}"/>
+    <hyperlink ref="E71" r:id="rId70" xr:uid="{3DD7E24A-7964-40E2-9A03-11731A0BF316}"/>
+    <hyperlink ref="E72" r:id="rId71" xr:uid="{815190F0-1FBE-4243-ABD5-950942ABC225}"/>
+    <hyperlink ref="E73" r:id="rId72" xr:uid="{1B32984C-52FE-4481-978E-07409B1FC0B6}"/>
+    <hyperlink ref="E74" r:id="rId73" xr:uid="{FCDC2AC8-B62D-4F24-936D-5D8A1B3C486F}"/>
+    <hyperlink ref="E75" r:id="rId74" xr:uid="{F74AD02E-6932-49CB-8D15-3F9BE7B6FAD5}"/>
+    <hyperlink ref="E76" r:id="rId75" xr:uid="{6DB0FBC1-A2FC-4992-8D02-88D1146D9E5B}"/>
+    <hyperlink ref="E77" r:id="rId76" xr:uid="{08CFB285-B096-4860-8D26-DE2357BBFF10}"/>
+    <hyperlink ref="E78" r:id="rId77" xr:uid="{72C08F11-BD1C-4FC1-8FC6-A3ECAB5821B7}"/>
+    <hyperlink ref="E79" r:id="rId78" xr:uid="{E634947A-3983-43B6-A09F-EEF76ECA103B}"/>
+    <hyperlink ref="E80" r:id="rId79" xr:uid="{BC84FC9C-B026-4647-A05F-196336FD71D2}"/>
+    <hyperlink ref="E81" r:id="rId80" xr:uid="{91A7A9B8-AE96-45BF-A966-E53E2DDD1021}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId49"/>
+  <pageSetup orientation="portrait" r:id="rId81"/>
 </worksheet>
 </file>
 
@@ -9416,7 +9760,7 @@
         <v>718</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="D42" s="11" t="s">
         <v>719</v>

--- a/data/geoparser_validation/geoparser_labelling_workbook.xlsx
+++ b/data/geoparser_validation/geoparser_labelling_workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\OneDrive\Desktop\Msc Data Science\Dissertation\Geoparser verification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{670AD2FD-D41A-424F-BEF6-452A9DB33148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45D5813-4B42-4F45-A9A3-BB740B125021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="911">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="932">
   <si>
     <t>ReliefWeb geoparser validation: labelling instructions</t>
   </si>
@@ -3388,6 +3388,69 @@
   </si>
   <si>
     <t>Report</t>
+  </si>
+  <si>
+    <t>Badhaadhe; Baki; Bandarbeyla; Belet Weyne; Borama; Buhoodle; Burtinle; Ceerigaabo (Erigavo); Dhahar; Dhuusamarreeb; Eyl; Gebiley (Gebilley); Hargeisa (Hargeysa); Kismaayo; Luuq; Qardho; Sheikh; Xudun</t>
+  </si>
+  <si>
+    <t>Afmadow; Baardheere; Baidoa; Berdale; Belet Weyne; Galkacyo; Jowhar; Kismayo</t>
+  </si>
+  <si>
+    <t>Hargeisa (Hafgeisa)</t>
+  </si>
+  <si>
+    <t>Adan Yabaal (Adan Yabaal / Adan Yabaal Rural); Balcad; Beletweyne (Beledweyne); Buloburte (Bulo Burti); Jalalaqsi; Jowhar; Mahas; Mataban (Matawaan / Matawan</t>
+  </si>
+  <si>
+    <t>assessment</t>
+  </si>
+  <si>
+    <t>Belet Weyne (Beletweyne); Bualle; Bulo Burte; Dollow; Hargeisa; Jowhar; Luuq</t>
+  </si>
+  <si>
+    <t>mogadishu</t>
+  </si>
+  <si>
+    <t>Adan Yabaal; Afgooye; Afmadow; Baardheere; Badhaadhe; Baki; Balcad; Banadir (Mogadishu); Bandarbeyla; Baydhaba (Baidoa); Belet Weyne; Belet Xaawo; Berbera; Borama; Bossaso; Bu'aale; Bulo Burto; Burco; Burtinle; Buuhoodle; Buur Hakaba; Cabudwaaq; Cadaado; Cadale; Caluula; Caynabo; Ceel Afweyn; Ceel Barde; Ceel Buur; Ceel Dheer; Ceel Waaq; Ceerigaabo; Dhuusamarreeb; Diinsoor; Doolow; Eyl; Gaalkacyo; Galdogob; Garbahaarey; Garoowe; Gebiley; Hargeysa; Hobyo; Iskushuban; Jalalaqsi; Jamaame; Jariiban; Jowhar; Kismaayo; Kurtunwaarey; Laas Caanood; Laasqoray; Lughaye; Luuq; Marka; Owdweyne; Qandala; Qansax Dheere; Qardho; Qoryooley; Rab Dhuure; Saakow; Sablaale; Salagle; Sheikh; Taleex; Tayeeglow; Waajid; Wanla Weyn; Xarardheere; Xudun; Xudur; Zeylac</t>
+  </si>
+  <si>
+    <t>Baardheere (Berdere); Baidoa; Belet Weyne; Berdale; Buur Hakaba (Burhakaba); Diinsoor; Mogadishu; Qansax Dheere (Qasadere); Qoryooley; Ufurow</t>
+  </si>
+  <si>
+    <t>Mogadishu, Jowhar</t>
+  </si>
+  <si>
+    <t>Afgooye; Afmadow; Baardheere (Berdere); Badhadhe (Badhaade); Baidoa; Baki; Balcad; Balanbale (Balanbal); Bandiradley; Baraawe (Barawe); Belet Hawa (Belet Xaawo); Belet Weyne (Beledweyne); Berdale (Berdele); Berbera; Borama; Bossaso; Bualle (Bu'aale); Bulo Burte (Bula Burde / Buloburte); Burco; Burdubo (Buurdhuubo / Buur Dhubo); Burhakaba (Buurhakaba); Cabudwaaq (Abduwaaq / Cabduwaaq); Cadaado (Adado / Caadado); Ceel Afweyn; Ceel Baraf; Ceel Barde (Elbarde / El Barde); Ceel Buur; Ceel Dheer (Ceeldheer / El Dheer); Ceel Waaq (Ceelwaaq / El Wak); Daynile (Daynille / Deynile); Dhahar; Dharkenley; Dhobley; Dhuusamarreeb (Dhuusamareeb); Diinsoor (Diinsor); Doolow (Dollow); Gaalkacyo (Galkayo / South Gaalkacyo / North Gaalkacyo); Garasbaley; Garbaharey (Garbaharrey); Gardo (Qardho); Garowe; Hargeysa; Hobyo; Jamame (Jamaame); Jariiban (Jariban / South Jariiban); Jalalaqsi (Jalaqsi / Jalalasi); Jowhar; Kahda (Khada / Kaxda); Kismayo (Kismaayo); Lughaya; Luuq; Mahaday; Mahas; Marka; Mataban; Mogadishu; Qansax Dheere (Qansaxdhere); Qardho; Qoryooley; Rabdhure (Rab Dhuure); Saakow (Sakow); Sheikh; Waajid (Wajid); Wajaale; Wisil; Xarardheere (Xarar Dheere / Xardheere); Xudur (Hudur); Zaylac (Zeila)</t>
+  </si>
+  <si>
+    <t>Awdheegle (Aw Dheegle); Burtinle; Buur Hakaba (cross-border mention); Galdogob; Wadajir</t>
+  </si>
+  <si>
+    <t>Awdheegle (Awdhegle); Baardheere; Baidoa (Baydhaba); Buula Mareer; Cabudwaaq; Daynile (Deynille); Gaalkacyo (Galkacayo); Galdogob; Janaale; Jariiban (Jariban); Jowhar; Kismayo; Marka; Qoryooley (Qoryole)</t>
+  </si>
+  <si>
+    <t>Afmadow; Belet Weyne (Beletweyne)</t>
+  </si>
+  <si>
+    <t>Afgooye; Baidoa; Belet Weyne; Cabudwaaq; Cadaado; Daynile (Danyile); Doolow; Dhuusamarreeb (Dhusamareeb); Gaalkacyo (Galkayo); Kahda (Khada); Qoryooley</t>
+  </si>
+  <si>
+    <t>Afgooye; Balcad; Belet Weyne</t>
+  </si>
+  <si>
+    <t>Afgooye; Baardheere; Baidoa; Baraawe; Belet Hawo (Belet Xaawo); Belet Weyne; Bossaso; Bulo Burte; Burco; Buuhoodle; Buur Hakaba; Cabudwaaq; Cadaado; Caynabo; Ceel Afweyn; Ceel Barde; Daynile (Dayniile); Dhobley; Dhuusamarreeb; Diinsoor; Doolow; Gaalkacyo (South Galkacyo / Galkacyo); Galdogob; Garbahaarey; Garowe; Hargeysa; Jalalaqsi; Jariiban (Jariban); Jowhar; Kahda (Khada); Kismayo (Kismaayo / Kismaayo North); Kurtunwaarey; Luuq; Marka; Mogadishu (Banadir); Qansax Dheere; Qardho; Qoryooley; Wanla Weyn; Waajid; Xudur</t>
+  </si>
+  <si>
+    <t>Afmadow; Burtinle; Laas Caanood</t>
+  </si>
+  <si>
+    <t>analysis</t>
+  </si>
+  <si>
+    <t>Afgooye; Afmadow; Baardheere; Baidoa; Balcad; Belet Weyne; Belet Xaawo; Dayniile; Doolow; Gaalkacyo; Garoowe; Hodan; Jamaame; Jowhar; Kahda; Kismaayo; Luuq</t>
+  </si>
+  <si>
+    <t>Afmadow (Dhobley FMP); Awdal / Borama (Harirad FMP); Bossaso; Buuhoodle; Cabudwaaq; Doolow; Zeylac (Lowyacado FMP)</t>
   </si>
 </sst>
 </file>
@@ -6982,7 +7045,7 @@
       <c r="D82" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="E82" s="7" t="s">
+      <c r="E82" s="13" t="s">
         <v>339</v>
       </c>
       <c r="F82" s="7" t="s">
@@ -6994,10 +7057,16 @@
       <c r="H82" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="I82" s="9"/>
-      <c r="J82" s="9"/>
+      <c r="I82" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="J82" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K82" s="9"/>
-      <c r="L82" s="9"/>
+      <c r="L82" s="9" t="s">
+        <v>880</v>
+      </c>
     </row>
     <row r="83" spans="1:12" ht="255" x14ac:dyDescent="0.45">
       <c r="A83" s="7">
@@ -7012,7 +7081,7 @@
       <c r="D83" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="E83" s="7" t="s">
+      <c r="E83" s="13" t="s">
         <v>342</v>
       </c>
       <c r="F83" s="7" t="s">
@@ -7024,10 +7093,16 @@
       <c r="H83" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="I83" s="9"/>
-      <c r="J83" s="9"/>
+      <c r="I83" s="14" t="s">
+        <v>911</v>
+      </c>
+      <c r="J83" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K83" s="9"/>
-      <c r="L83" s="9"/>
+      <c r="L83" s="9" t="s">
+        <v>910</v>
+      </c>
     </row>
     <row r="84" spans="1:12" ht="153" x14ac:dyDescent="0.45">
       <c r="A84" s="7">
@@ -7042,7 +7117,7 @@
       <c r="D84" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="E84" s="7" t="s">
+      <c r="E84" s="13" t="s">
         <v>345</v>
       </c>
       <c r="F84" s="7" t="s">
@@ -7054,10 +7129,16 @@
       <c r="H84" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="I84" s="9"/>
-      <c r="J84" s="9"/>
+      <c r="I84" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="J84" s="9" t="s">
+        <v>616</v>
+      </c>
       <c r="K84" s="9"/>
-      <c r="L84" s="9"/>
+      <c r="L84" s="9" t="s">
+        <v>880</v>
+      </c>
     </row>
     <row r="85" spans="1:12" ht="191.25" x14ac:dyDescent="0.45">
       <c r="A85" s="7">
@@ -7072,7 +7153,7 @@
       <c r="D85" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="E85" s="7" t="s">
+      <c r="E85" s="13" t="s">
         <v>349</v>
       </c>
       <c r="F85" s="7" t="s">
@@ -7084,10 +7165,16 @@
       <c r="H85" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="I85" s="9"/>
-      <c r="J85" s="9"/>
+      <c r="I85" s="14" t="s">
+        <v>912</v>
+      </c>
+      <c r="J85" s="9" t="s">
+        <v>913</v>
+      </c>
       <c r="K85" s="9"/>
-      <c r="L85" s="9"/>
+      <c r="L85" s="9" t="s">
+        <v>874</v>
+      </c>
     </row>
     <row r="86" spans="1:12" ht="255" x14ac:dyDescent="0.45">
       <c r="A86" s="7">
@@ -7102,7 +7189,7 @@
       <c r="D86" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="E86" s="7" t="s">
+      <c r="E86" s="13" t="s">
         <v>353</v>
       </c>
       <c r="F86" s="7" t="s">
@@ -7114,10 +7201,16 @@
       <c r="H86" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="I86" s="9"/>
-      <c r="J86" s="9"/>
+      <c r="I86" s="14" t="s">
+        <v>914</v>
+      </c>
+      <c r="J86" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K86" s="9"/>
-      <c r="L86" s="9"/>
+      <c r="L86" s="9" t="s">
+        <v>915</v>
+      </c>
     </row>
     <row r="87" spans="1:12" ht="191.25" x14ac:dyDescent="0.45">
       <c r="A87" s="7">
@@ -7132,7 +7225,7 @@
       <c r="D87" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="E87" s="7" t="s">
+      <c r="E87" s="13" t="s">
         <v>356</v>
       </c>
       <c r="F87" s="7" t="s">
@@ -7144,10 +7237,16 @@
       <c r="H87" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="I87" s="9"/>
-      <c r="J87" s="9"/>
+      <c r="I87" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="J87" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K87" s="9"/>
-      <c r="L87" s="9"/>
+      <c r="L87" s="9" t="s">
+        <v>880</v>
+      </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A88" s="7">
@@ -7162,7 +7261,7 @@
       <c r="D88" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="E88" s="7" t="s">
+      <c r="E88" s="13" t="s">
         <v>359</v>
       </c>
       <c r="F88" s="7" t="s">
@@ -7172,10 +7271,16 @@
         <v>46</v>
       </c>
       <c r="H88" s="8"/>
-      <c r="I88" s="9"/>
-      <c r="J88" s="9"/>
+      <c r="I88" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="J88" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K88" s="9"/>
-      <c r="L88" s="9"/>
+      <c r="L88" s="9" t="s">
+        <v>877</v>
+      </c>
     </row>
     <row r="89" spans="1:12" ht="178.5" x14ac:dyDescent="0.45">
       <c r="A89" s="7">
@@ -7190,7 +7295,7 @@
       <c r="D89" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="E89" s="7" t="s">
+      <c r="E89" s="13" t="s">
         <v>361</v>
       </c>
       <c r="F89" s="7" t="s">
@@ -7202,12 +7307,18 @@
       <c r="H89" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="I89" s="9"/>
-      <c r="J89" s="9"/>
+      <c r="I89" s="14" t="s">
+        <v>916</v>
+      </c>
+      <c r="J89" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K89" s="9"/>
-      <c r="L89" s="9"/>
-    </row>
-    <row r="90" spans="1:12" ht="178.5" x14ac:dyDescent="0.45">
+      <c r="L89" s="9" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="191.25" x14ac:dyDescent="0.45">
       <c r="A90" s="7">
         <v>88</v>
       </c>
@@ -7220,7 +7331,7 @@
       <c r="D90" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="E90" s="7" t="s">
+      <c r="E90" s="13" t="s">
         <v>365</v>
       </c>
       <c r="F90" s="7" t="s">
@@ -7232,12 +7343,18 @@
       <c r="H90" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="I90" s="9"/>
-      <c r="J90" s="9"/>
+      <c r="I90" s="9" t="s">
+        <v>917</v>
+      </c>
+      <c r="J90" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K90" s="9"/>
-      <c r="L90" s="9"/>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="L90" s="9" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="395.25" x14ac:dyDescent="0.45">
       <c r="A91" s="7">
         <v>89</v>
       </c>
@@ -7250,7 +7367,7 @@
       <c r="D91" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="E91" s="7" t="s">
+      <c r="E91" s="13" t="s">
         <v>369</v>
       </c>
       <c r="F91" s="7" t="s">
@@ -7260,10 +7377,16 @@
         <v>46</v>
       </c>
       <c r="H91" s="8"/>
-      <c r="I91" s="9"/>
-      <c r="J91" s="9"/>
+      <c r="I91" s="14" t="s">
+        <v>918</v>
+      </c>
+      <c r="J91" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K91" s="9"/>
-      <c r="L91" s="9"/>
+      <c r="L91" s="9" t="s">
+        <v>877</v>
+      </c>
     </row>
     <row r="92" spans="1:12" ht="102" x14ac:dyDescent="0.45">
       <c r="A92" s="7">
@@ -7278,7 +7401,7 @@
       <c r="D92" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="E92" s="7" t="s">
+      <c r="E92" s="13" t="s">
         <v>371</v>
       </c>
       <c r="F92" s="7" t="s">
@@ -7290,10 +7413,16 @@
       <c r="H92" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="I92" s="9"/>
-      <c r="J92" s="9"/>
+      <c r="I92" s="14" t="s">
+        <v>919</v>
+      </c>
+      <c r="J92" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K92" s="9"/>
-      <c r="L92" s="9"/>
+      <c r="L92" s="9" t="s">
+        <v>874</v>
+      </c>
     </row>
     <row r="93" spans="1:12" ht="191.25" x14ac:dyDescent="0.45">
       <c r="A93" s="7">
@@ -7308,7 +7437,7 @@
       <c r="D93" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="E93" s="7" t="s">
+      <c r="E93" s="13" t="s">
         <v>374</v>
       </c>
       <c r="F93" s="7" t="s">
@@ -7320,12 +7449,18 @@
       <c r="H93" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="I93" s="9"/>
-      <c r="J93" s="9"/>
+      <c r="I93" s="9" t="s">
+        <v>920</v>
+      </c>
+      <c r="J93" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K93" s="9"/>
-      <c r="L93" s="9"/>
-    </row>
-    <row r="94" spans="1:12" ht="242.25" x14ac:dyDescent="0.45">
+      <c r="L93" s="9" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="409.5" x14ac:dyDescent="0.45">
       <c r="A94" s="7">
         <v>92</v>
       </c>
@@ -7338,7 +7473,7 @@
       <c r="D94" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="E94" s="7" t="s">
+      <c r="E94" s="13" t="s">
         <v>378</v>
       </c>
       <c r="F94" s="7" t="s">
@@ -7350,10 +7485,16 @@
       <c r="H94" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="I94" s="9"/>
-      <c r="J94" s="9"/>
+      <c r="I94" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="J94" s="14" t="s">
+        <v>922</v>
+      </c>
       <c r="K94" s="9"/>
-      <c r="L94" s="9"/>
+      <c r="L94" s="9" t="s">
+        <v>874</v>
+      </c>
     </row>
     <row r="95" spans="1:12" ht="165.75" x14ac:dyDescent="0.45">
       <c r="A95" s="7">
@@ -7368,7 +7509,7 @@
       <c r="D95" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="E95" s="7" t="s">
+      <c r="E95" s="13" t="s">
         <v>382</v>
       </c>
       <c r="F95" s="7" t="s">
@@ -7380,10 +7521,16 @@
       <c r="H95" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="I95" s="9"/>
-      <c r="J95" s="9"/>
+      <c r="I95" s="14" t="s">
+        <v>923</v>
+      </c>
+      <c r="J95" s="14" t="s">
+        <v>924</v>
+      </c>
       <c r="K95" s="9"/>
-      <c r="L95" s="9"/>
+      <c r="L95" s="9" t="s">
+        <v>874</v>
+      </c>
     </row>
     <row r="96" spans="1:12" ht="127.5" x14ac:dyDescent="0.45">
       <c r="A96" s="7">
@@ -7398,7 +7545,7 @@
       <c r="D96" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="E96" s="7" t="s">
+      <c r="E96" s="13" t="s">
         <v>386</v>
       </c>
       <c r="F96" s="7" t="s">
@@ -7410,10 +7557,16 @@
       <c r="H96" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="I96" s="9"/>
-      <c r="J96" s="9"/>
+      <c r="I96" s="14" t="s">
+        <v>923</v>
+      </c>
+      <c r="J96" s="14" t="s">
+        <v>924</v>
+      </c>
       <c r="K96" s="9"/>
-      <c r="L96" s="9"/>
+      <c r="L96" s="9" t="s">
+        <v>874</v>
+      </c>
     </row>
     <row r="97" spans="1:12" ht="89.25" x14ac:dyDescent="0.45">
       <c r="A97" s="7">
@@ -7428,7 +7581,7 @@
       <c r="D97" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="E97" s="7" t="s">
+      <c r="E97" s="13" t="s">
         <v>390</v>
       </c>
       <c r="F97" s="7" t="s">
@@ -7440,10 +7593,16 @@
       <c r="H97" s="8" t="s">
         <v>391</v>
       </c>
-      <c r="I97" s="9"/>
-      <c r="J97" s="9"/>
+      <c r="I97" s="14" t="s">
+        <v>925</v>
+      </c>
+      <c r="J97" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K97" s="9"/>
-      <c r="L97" s="9"/>
+      <c r="L97" s="9" t="s">
+        <v>874</v>
+      </c>
     </row>
     <row r="98" spans="1:12" ht="102" x14ac:dyDescent="0.45">
       <c r="A98" s="7">
@@ -7458,7 +7617,7 @@
       <c r="D98" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="E98" s="7" t="s">
+      <c r="E98" s="13" t="s">
         <v>393</v>
       </c>
       <c r="F98" s="7" t="s">
@@ -7470,10 +7629,16 @@
       <c r="H98" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="I98" s="9"/>
-      <c r="J98" s="9"/>
+      <c r="I98" s="9" t="s">
+        <v>926</v>
+      </c>
+      <c r="J98" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K98" s="9"/>
-      <c r="L98" s="9"/>
+      <c r="L98" s="9" t="s">
+        <v>915</v>
+      </c>
     </row>
     <row r="99" spans="1:12" ht="178.5" x14ac:dyDescent="0.45">
       <c r="A99" s="7">
@@ -7488,7 +7653,7 @@
       <c r="D99" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="E99" s="7" t="s">
+      <c r="E99" s="13" t="s">
         <v>396</v>
       </c>
       <c r="F99" s="7" t="s">
@@ -7500,10 +7665,16 @@
       <c r="H99" s="8" t="s">
         <v>397</v>
       </c>
-      <c r="I99" s="9"/>
-      <c r="J99" s="9"/>
+      <c r="I99" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="J99" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K99" s="9"/>
-      <c r="L99" s="9"/>
+      <c r="L99" s="9" t="s">
+        <v>929</v>
+      </c>
     </row>
     <row r="100" spans="1:12" ht="306" x14ac:dyDescent="0.45">
       <c r="A100" s="7">
@@ -7518,7 +7689,7 @@
       <c r="D100" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="E100" s="7" t="s">
+      <c r="E100" s="13" t="s">
         <v>400</v>
       </c>
       <c r="F100" s="7" t="s">
@@ -7530,10 +7701,16 @@
       <c r="H100" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="I100" s="9"/>
-      <c r="J100" s="9"/>
+      <c r="I100" s="14" t="s">
+        <v>927</v>
+      </c>
+      <c r="J100" s="9" t="s">
+        <v>928</v>
+      </c>
       <c r="K100" s="9"/>
-      <c r="L100" s="9"/>
+      <c r="L100" s="9" t="s">
+        <v>885</v>
+      </c>
     </row>
     <row r="101" spans="1:12" ht="153" x14ac:dyDescent="0.45">
       <c r="A101" s="7">
@@ -7548,7 +7725,7 @@
       <c r="D101" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="E101" s="7" t="s">
+      <c r="E101" s="13" t="s">
         <v>404</v>
       </c>
       <c r="F101" s="7" t="s">
@@ -7560,10 +7737,16 @@
       <c r="H101" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="I101" s="9"/>
-      <c r="J101" s="9"/>
+      <c r="I101" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="J101" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K101" s="9"/>
-      <c r="L101" s="9"/>
+      <c r="L101" s="9" t="s">
+        <v>874</v>
+      </c>
     </row>
     <row r="102" spans="1:12" ht="140.25" x14ac:dyDescent="0.45">
       <c r="A102" s="7">
@@ -7578,7 +7761,7 @@
       <c r="D102" s="7" t="s">
         <v>407</v>
       </c>
-      <c r="E102" s="7" t="s">
+      <c r="E102" s="13" t="s">
         <v>408</v>
       </c>
       <c r="F102" s="7" t="s">
@@ -7590,10 +7773,16 @@
       <c r="H102" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="I102" s="9"/>
-      <c r="J102" s="9"/>
+      <c r="I102" s="14" t="s">
+        <v>930</v>
+      </c>
+      <c r="J102" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K102" s="9"/>
-      <c r="L102" s="9"/>
+      <c r="L102" s="9" t="s">
+        <v>874</v>
+      </c>
     </row>
     <row r="103" spans="1:12" ht="102" x14ac:dyDescent="0.45">
       <c r="A103" s="7">
@@ -7608,7 +7797,7 @@
       <c r="D103" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="E103" s="7" t="s">
+      <c r="E103" s="13" t="s">
         <v>412</v>
       </c>
       <c r="F103" s="7" t="s">
@@ -7620,10 +7809,16 @@
       <c r="H103" s="8" t="s">
         <v>413</v>
       </c>
-      <c r="I103" s="9"/>
-      <c r="J103" s="9"/>
+      <c r="I103" s="14" t="s">
+        <v>931</v>
+      </c>
+      <c r="J103" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K103" s="9"/>
-      <c r="L103" s="9"/>
+      <c r="L103" s="9" t="s">
+        <v>885</v>
+      </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A104" s="7">
@@ -7638,7 +7833,7 @@
       <c r="D104" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="E104" s="7" t="s">
+      <c r="E104" s="13" t="s">
         <v>416</v>
       </c>
       <c r="F104" s="7" t="s">
@@ -7648,10 +7843,16 @@
         <v>46</v>
       </c>
       <c r="H104" s="8"/>
-      <c r="I104" s="9"/>
-      <c r="J104" s="9"/>
+      <c r="I104" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="J104" s="9" t="s">
+        <v>815</v>
+      </c>
       <c r="K104" s="9"/>
-      <c r="L104" s="9"/>
+      <c r="L104" s="9" t="s">
+        <v>877</v>
+      </c>
     </row>
     <row r="105" spans="1:12" ht="178.5" x14ac:dyDescent="0.45">
       <c r="A105" s="7">
@@ -9161,9 +9362,32 @@
     <hyperlink ref="E79" r:id="rId78" xr:uid="{E634947A-3983-43B6-A09F-EEF76ECA103B}"/>
     <hyperlink ref="E80" r:id="rId79" xr:uid="{BC84FC9C-B026-4647-A05F-196336FD71D2}"/>
     <hyperlink ref="E81" r:id="rId80" xr:uid="{91A7A9B8-AE96-45BF-A966-E53E2DDD1021}"/>
+    <hyperlink ref="E82" r:id="rId81" xr:uid="{D0587C85-1001-4253-BB34-719A6610CCE3}"/>
+    <hyperlink ref="E83" r:id="rId82" xr:uid="{D6F44159-AD96-4BCF-BEBF-021EF994AB83}"/>
+    <hyperlink ref="E84" r:id="rId83" xr:uid="{FB428AD3-FB44-4485-B155-7251649F850B}"/>
+    <hyperlink ref="E85" r:id="rId84" xr:uid="{97346685-CB0A-4070-A750-6B453C89C42B}"/>
+    <hyperlink ref="E86" r:id="rId85" xr:uid="{E4881594-FB70-473F-BC9F-622C54EB4BC1}"/>
+    <hyperlink ref="E87" r:id="rId86" xr:uid="{A3A8DCE4-5313-4F27-9C4F-820226C4646D}"/>
+    <hyperlink ref="E88" r:id="rId87" xr:uid="{EF4B8E78-C051-4DF1-949A-93CD276299CA}"/>
+    <hyperlink ref="E89" r:id="rId88" xr:uid="{AA68AE43-0A80-4370-8259-C5DD7C63EF53}"/>
+    <hyperlink ref="E90" r:id="rId89" xr:uid="{EFBA5355-8969-41B9-867A-657C8CDEBEC0}"/>
+    <hyperlink ref="E91" r:id="rId90" xr:uid="{898389D9-641A-42B2-AD81-7911168B1F9F}"/>
+    <hyperlink ref="E92" r:id="rId91" xr:uid="{4C1D85C6-2855-4D5C-9131-4F70F1610417}"/>
+    <hyperlink ref="E93" r:id="rId92" xr:uid="{2A5154C2-3DCC-44EF-B873-3DF6616F51CD}"/>
+    <hyperlink ref="E94" r:id="rId93" xr:uid="{9149C321-623B-42F6-9F3B-E88885EBBEE1}"/>
+    <hyperlink ref="E95" r:id="rId94" xr:uid="{49804D41-5D23-46B8-91AC-BC6FA712A28C}"/>
+    <hyperlink ref="E96" r:id="rId95" xr:uid="{9EC6D9E3-6A6D-4A5E-8B36-C2CD89197F3F}"/>
+    <hyperlink ref="E97" r:id="rId96" xr:uid="{1D30A2D3-53F8-4ACA-9B37-462F8469FA57}"/>
+    <hyperlink ref="E98" r:id="rId97" xr:uid="{7FACF88D-52A9-4CD4-B07C-612394B76C71}"/>
+    <hyperlink ref="E99" r:id="rId98" xr:uid="{CE189AA5-4E61-4160-9722-DC968577D16C}"/>
+    <hyperlink ref="E100" r:id="rId99" xr:uid="{7F370221-D280-4456-A880-16FCAC5A81CB}"/>
+    <hyperlink ref="E101" r:id="rId100" xr:uid="{37487281-8416-4D2D-86CD-85E3782E78B8}"/>
+    <hyperlink ref="E102" r:id="rId101" xr:uid="{A6688A67-D5A4-42AD-B3D2-2BB37B3883FB}"/>
+    <hyperlink ref="E103" r:id="rId102" xr:uid="{C196CB98-8A24-4F45-903E-D5B0E9C81F54}"/>
+    <hyperlink ref="E104" r:id="rId103" xr:uid="{E5110DED-17DD-4A0E-B79E-1D80C5DAA51A}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId81"/>
+  <pageSetup orientation="portrait" r:id="rId104"/>
 </worksheet>
 </file>
 
